--- a/基本設計/11_従業員と部門_API基本設計書.xlsx
+++ b/基本設計/11_従業員と部門_API基本設計書.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R139344f9931b4a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R9c9f090cca004235"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="Rbf1e1df818984ad2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="21" r:id="R76d0d4480cdc4843"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R2143158fbd804bf8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R8b767919be4b448f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_従業員Excel仕様" sheetId="24" r:id="Ref4892aa3e7e449a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="R70b36c20615e47ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="R96b6abc3bd5b4cb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="27" r:id="R4e125fd5886947f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R1fb71cf1e2134417"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R2c3a3254de4b42aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R015202d1460948cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="21" r:id="R66f2147fa5bb4748"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="Re2d14e1c9e47423f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R0b9f0a98b0064f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_従業員Excel仕様" sheetId="24" r:id="R61a54652e7234274"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="Rf8edeb17628b45be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="Rdb65117bb87746c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="27" r:id="R2daa254ba06c4e10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1298,10 +1298,7 @@
       <x:c r="F16" s="196"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1317,25 +1314,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="240" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="240"/>
-      <x:c r="D19" s="240"/>
-      <x:c r="E19" s="240"/>
-      <x:c r="F19" s="240"/>
-      <x:c r="G19" s="240"/>
-      <x:c r="H19" s="240"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="240"/>
-      <x:c r="C20" s="240"/>
-      <x:c r="D20" s="240"/>
-      <x:c r="E20" s="240"/>
-      <x:c r="F20" s="240"/>
-      <x:c r="G20" s="240"/>
-      <x:c r="H20" s="240"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="240"/>
@@ -3450,17 +3444,15 @@
       <x:c r="I20" s="64"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="88" t="str">
-        <x:v>Class名、Method名、SQLは詳細設計で定義する。ただし本SheetのURL、I/O、権限、Data範囲、Error契約はPG判断で変更しない。</x:v>
-      </x:c>
-      <x:c r="B21" s="89"/>
-      <x:c r="C21" s="89"/>
-      <x:c r="D21" s="89"/>
-      <x:c r="E21" s="89"/>
-      <x:c r="F21" s="89"/>
-      <x:c r="G21" s="89"/>
-      <x:c r="H21" s="89"/>
-      <x:c r="I21" s="90"/>
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
+      <x:c r="I21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="91"/>

--- a/基本設計/11_従業員と部門_API基本設計書.xlsx
+++ b/基本設計/11_従業員と部門_API基本設計書.xlsx
@@ -2,16 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R1fb71cf1e2134417"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R2c3a3254de4b42aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R015202d1460948cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="21" r:id="R66f2147fa5bb4748"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="Re2d14e1c9e47423f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R0b9f0a98b0064f24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_従業員Excel仕様" sheetId="24" r:id="R61a54652e7234274"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="Rf8edeb17628b45be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="Rdb65117bb87746c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="27" r:id="R2daa254ba06c4e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R7c11ed0e89624cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rc0896ebe005c45f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R948295cfd5184c7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R995024f30be14e7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R8ebc68080ff24aa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_従業員Excel仕様" sheetId="24" r:id="R72afb8a67f734984"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="Reb20bbbae6ce4a76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="Raba826ac57904bb0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -164,8 +162,19 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF18283A"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF193C61"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="29">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -307,8 +316,18 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234F77"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F5FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -366,11 +385,25 @@
         <x:color rgb="FFA6A6A6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="241">
+  <x:cellXfs count="259">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -868,6 +901,56 @@
     <x:xf numFmtId="0" fontId="24" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="30" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1166,7 +1249,36 @@
     <x:col min="26" max="26" width="3" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1"/>
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+    </x:row>
     <x:row r="3">
+      <x:c r="A3"/>
       <x:c r="B3" s="227" t="str">
         <x:v>Company WorkHub
 企業従業員・タスク管理システム</x:v>
@@ -1177,8 +1289,13 @@
       <x:c r="F3" s="227"/>
       <x:c r="G3" s="227"/>
       <x:c r="H3" s="227"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4"/>
       <x:c r="B4" s="227"/>
       <x:c r="C4" s="227"/>
       <x:c r="D4" s="227"/>
@@ -1186,8 +1303,13 @@
       <x:c r="F4" s="227"/>
       <x:c r="G4" s="227"/>
       <x:c r="H4" s="227"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5"/>
       <x:c r="B5" s="227"/>
       <x:c r="C5" s="227"/>
       <x:c r="D5" s="227"/>
@@ -1195,8 +1317,13 @@
       <x:c r="F5" s="227"/>
       <x:c r="G5" s="227"/>
       <x:c r="H5" s="227"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6"/>
       <x:c r="B6"/>
       <x:c r="C6"/>
       <x:c r="D6"/>
@@ -1204,8 +1331,27 @@
       <x:c r="F6"/>
       <x:c r="G6"/>
       <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
+      <x:c r="A8"/>
       <x:c r="B8" s="233" t="str">
         <x:v>従業員と部門 API基本設計書</x:v>
       </x:c>
@@ -1215,8 +1361,13 @@
       <x:c r="F8" s="233"/>
       <x:c r="G8" s="233"/>
       <x:c r="H8" s="233"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
+      <x:c r="A9"/>
       <x:c r="B9" s="233"/>
       <x:c r="C9" s="233"/>
       <x:c r="D9" s="233"/>
@@ -1224,8 +1375,13 @@
       <x:c r="F9" s="233"/>
       <x:c r="G9" s="233"/>
       <x:c r="H9" s="233"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
+      <x:c r="A10"/>
       <x:c r="B10" s="233"/>
       <x:c r="C10" s="233"/>
       <x:c r="D10" s="233"/>
@@ -1233,49 +1389,84 @@
       <x:c r="F10" s="233"/>
       <x:c r="G10" s="233"/>
       <x:c r="H10" s="233"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
+      <x:c r="A11"/>
       <x:c r="B11"/>
-      <x:c r="C11" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C11" s="203" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
       <x:c r="F11"/>
       <x:c r="G11"/>
       <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" s="235" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12" s="244" t="str">
+        <x:v>Document ID</x:v>
       </x:c>
       <x:c r="D12" s="196" t="str">
         <x:v>CW-BD-API-ORG</x:v>
       </x:c>
       <x:c r="E12" s="196"/>
       <x:c r="F12" s="196"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
       <x:c r="C13" s="235" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="D13" s="196" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="D13" s="245" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="E13" s="196"/>
       <x:c r="F13" s="196"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
       <x:c r="C14" s="235" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="D14" s="196" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="D14" s="245" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E14" s="196"/>
       <x:c r="F14" s="196"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
       <x:c r="C15" s="235" t="str">
         <x:v>作成者</x:v>
       </x:c>
@@ -1284,6 +1475,12 @@
       </x:c>
       <x:c r="E15" s="196"/>
       <x:c r="F15" s="196"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
@@ -1291,24 +1488,35 @@
       <x:c r="C16" s="235" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="D16" s="196" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="D16" s="245" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="E16" s="196"/>
       <x:c r="F16" s="196"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="247"/>
+      <x:c r="B17" s="247"/>
+      <x:c r="C17" s="247"/>
+      <x:c r="D17" s="247"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="247"/>
+      <x:c r="B18" s="247"/>
+      <x:c r="C18" s="247" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="D18" s="247" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
@@ -1375,366 +1583,6 @@
     <x:mergeCell ref="D15:F15"/>
     <x:mergeCell ref="D16:F16"/>
     <x:mergeCell ref="B19:H21"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="62" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="138" t="str">
-        <x:v>API権限対応</x:v>
-      </x:c>
-      <x:c r="B1" s="138"/>
-      <x:c r="C1" s="138"/>
-      <x:c r="D1" s="138"/>
-      <x:c r="E1" s="138"/>
-      <x:c r="F1" s="138"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="138"/>
-      <x:c r="B2" s="138"/>
-      <x:c r="C2" s="138"/>
-      <x:c r="D2" s="138"/>
-      <x:c r="E2" s="138"/>
-      <x:c r="F2" s="138"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="141" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="141" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="D3" s="139" t="str">
-        <x:v>CW-BD-11-PERM</x:v>
-      </x:c>
-      <x:c r="E3" s="139"/>
-      <x:c r="F3" s="139"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="141" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="141" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="D4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="E4" s="139"/>
-      <x:c r="F4" s="139"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="142" t="str">
-        <x:v>1. API・Permission・Data範囲</x:v>
-      </x:c>
-      <x:c r="B6" s="142"/>
-      <x:c r="C6" s="142"/>
-      <x:c r="D6" s="142"/>
-      <x:c r="E6" s="142"/>
-      <x:c r="F6" s="142"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="147" t="str">
-        <x:v>API ID</x:v>
-      </x:c>
-      <x:c r="B7" s="147" t="str">
-        <x:v>API名</x:v>
-      </x:c>
-      <x:c r="C7" s="147" t="str">
-        <x:v>Permission Code</x:v>
-      </x:c>
-      <x:c r="D7" s="147" t="str">
-        <x:v>許可Role</x:v>
-      </x:c>
-      <x:c r="E7" s="147" t="str">
-        <x:v>Data範囲</x:v>
-      </x:c>
-      <x:c r="F7" s="147" t="str">
-        <x:v>判定方式</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="151" t="str">
-        <x:v>API-EMP-001</x:v>
-      </x:c>
-      <x:c r="B8" s="151" t="str">
-        <x:v>従業員ページ検索</x:v>
-      </x:c>
-      <x:c r="C8" s="151" t="str">
-        <x:v>PERM-EMP-READ</x:v>
-      </x:c>
-      <x:c r="D8" s="151" t="str">
-        <x:v>管理者/PM</x:v>
-      </x:c>
-      <x:c r="E8" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ関係社員</x:v>
-      </x:c>
-      <x:c r="F8" s="151" t="str">
-        <x:v>hasAuthority('PERM-EMP-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="151" t="str">
-        <x:v>API-EMP-002</x:v>
-      </x:c>
-      <x:c r="B9" s="151" t="str">
-        <x:v>従業員詳細</x:v>
-      </x:c>
-      <x:c r="C9" s="151" t="str">
-        <x:v>PERM-EMP-READ</x:v>
-      </x:c>
-      <x:c r="D9" s="151" t="str">
-        <x:v>管理者/PM</x:v>
-      </x:c>
-      <x:c r="E9" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ関係社員</x:v>
-      </x:c>
-      <x:c r="F9" s="151" t="str">
-        <x:v>hasAuthority('PERM-EMP-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="151" t="str">
-        <x:v>API-EMP-003</x:v>
-      </x:c>
-      <x:c r="B10" s="151" t="str">
-        <x:v>従業員登録</x:v>
-      </x:c>
-      <x:c r="C10" s="151" t="str">
-        <x:v>PERM-EMP-WRITE</x:v>
-      </x:c>
-      <x:c r="D10" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E10" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F10" s="151" t="str">
-        <x:v>hasAuthority('PERM-EMP-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="151" t="str">
-        <x:v>API-EMP-004</x:v>
-      </x:c>
-      <x:c r="B11" s="151" t="str">
-        <x:v>従業員更新</x:v>
-      </x:c>
-      <x:c r="C11" s="151" t="str">
-        <x:v>PERM-EMP-WRITE</x:v>
-      </x:c>
-      <x:c r="D11" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E11" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F11" s="151" t="str">
-        <x:v>hasAuthority('PERM-EMP-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="151" t="str">
-        <x:v>API-EMP-005</x:v>
-      </x:c>
-      <x:c r="B12" s="151" t="str">
-        <x:v>従業員状態変更</x:v>
-      </x:c>
-      <x:c r="C12" s="151" t="str">
-        <x:v>PERM-EMP-WRITE</x:v>
-      </x:c>
-      <x:c r="D12" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E12" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F12" s="151" t="str">
-        <x:v>hasAuthority('PERM-EMP-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="151" t="str">
-        <x:v>API-EMP-006</x:v>
-      </x:c>
-      <x:c r="B13" s="151" t="str">
-        <x:v>従業員Excel取込</x:v>
-      </x:c>
-      <x:c r="C13" s="151" t="str">
-        <x:v>PERM-EMP-WRITE</x:v>
-      </x:c>
-      <x:c r="D13" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E13" s="151" t="str">
-        <x:v>管理者のみ; 全件検証後一括Commit</x:v>
-      </x:c>
-      <x:c r="F13" s="151" t="str">
-        <x:v>hasAuthority('PERM-EMP-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="151" t="str">
-        <x:v>API-EMP-007</x:v>
-      </x:c>
-      <x:c r="B14" s="151" t="str">
-        <x:v>従業員Excel出力</x:v>
-      </x:c>
-      <x:c r="C14" s="151" t="str">
-        <x:v>PERM-EMP-READ</x:v>
-      </x:c>
-      <x:c r="D14" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E14" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F14" s="151" t="str">
-        <x:v>hasAuthority('PERM-EMP-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="151" t="str">
-        <x:v>API-DEPT-001</x:v>
-      </x:c>
-      <x:c r="B15" s="151" t="str">
-        <x:v>部門Tree取得</x:v>
-      </x:c>
-      <x:c r="C15" s="151" t="str">
-        <x:v>-（認証済共通）</x:v>
-      </x:c>
-      <x:c r="D15" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E15" s="151" t="str">
-        <x:v>一般=有効部門, 管理者=指定可</x:v>
-      </x:c>
-      <x:c r="F15" s="151" t="str">
-        <x:v>認証・本人/共通条件をServiceで判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="151" t="str">
-        <x:v>API-DEPT-002</x:v>
-      </x:c>
-      <x:c r="B16" s="151" t="str">
-        <x:v>部門詳細</x:v>
-      </x:c>
-      <x:c r="C16" s="151" t="str">
-        <x:v>PERM-DEPT-WRITE</x:v>
-      </x:c>
-      <x:c r="D16" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E16" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F16" s="151" t="str">
-        <x:v>hasAuthority('PERM-DEPT-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="151" t="str">
-        <x:v>API-DEPT-003</x:v>
-      </x:c>
-      <x:c r="B17" s="151" t="str">
-        <x:v>部門登録</x:v>
-      </x:c>
-      <x:c r="C17" s="151" t="str">
-        <x:v>PERM-DEPT-WRITE</x:v>
-      </x:c>
-      <x:c r="D17" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E17" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F17" s="151" t="str">
-        <x:v>hasAuthority('PERM-DEPT-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="151" t="str">
-        <x:v>API-DEPT-004</x:v>
-      </x:c>
-      <x:c r="B18" s="151" t="str">
-        <x:v>部門更新</x:v>
-      </x:c>
-      <x:c r="C18" s="151" t="str">
-        <x:v>PERM-DEPT-WRITE</x:v>
-      </x:c>
-      <x:c r="D18" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E18" s="151" t="str">
-        <x:v>自己・子孫を親に設定不可</x:v>
-      </x:c>
-      <x:c r="F18" s="151" t="str">
-        <x:v>hasAuthority('PERM-DEPT-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="151" t="str">
-        <x:v>API-DEPT-005</x:v>
-      </x:c>
-      <x:c r="B19" s="151" t="str">
-        <x:v>部門削除</x:v>
-      </x:c>
-      <x:c r="C19" s="151" t="str">
-        <x:v>PERM-DEPT-WRITE</x:v>
-      </x:c>
-      <x:c r="D19" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E19" s="151" t="str">
-        <x:v>社員・子部門・PJ関連なし</x:v>
-      </x:c>
-      <x:c r="F19" s="151" t="str">
-        <x:v>hasAuthority('PERM-DEPT-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="155" t="str">
-        <x:v>ControllerのRole表示だけで認可しない。Service層でPermission Code、本人/PJ Member/担当PM等のData範囲、対象Dataの存在を再判定する。</x:v>
-      </x:c>
-      <x:c r="B21" s="155"/>
-      <x:c r="C21" s="155"/>
-      <x:c r="D21" s="155"/>
-      <x:c r="E21" s="155"/>
-      <x:c r="F21" s="155"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="155"/>
-      <x:c r="B22" s="155"/>
-      <x:c r="C22" s="155"/>
-      <x:c r="D22" s="155"/>
-      <x:c r="E22" s="155"/>
-      <x:c r="F22" s="155"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:F2"/>
-    <x:mergeCell ref="A6:F6"/>
-    <x:mergeCell ref="A21:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1765,6 +1613,10 @@
       <x:c r="F1" s="172"/>
       <x:c r="G1" s="172"/>
       <x:c r="H1" s="172"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="172"/>
@@ -1775,42 +1627,42 @@
       <x:c r="F2" s="172"/>
       <x:c r="G2" s="172"/>
       <x:c r="H2" s="172"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="174" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="139"/>
-      <x:c r="D3" s="174" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="139" t="str">
-        <x:v>DOCUMENT-REVISION</x:v>
-      </x:c>
-      <x:c r="F3" s="139"/>
-      <x:c r="G3" s="139"/>
-      <x:c r="H3" s="139"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="174" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="139"/>
-      <x:c r="D4" s="174" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="139"/>
-      <x:c r="G4" s="139"/>
-      <x:c r="H4" s="139"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="248" t="str">
+        <x:v>システム名：Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="63"/>
+      <x:c r="C3" s="63"/>
+      <x:c r="D3" s="248"/>
+      <x:c r="E3" s="63"/>
+      <x:c r="F3" s="63"/>
+      <x:c r="G3" s="63"/>
+      <x:c r="H3" s="63"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="248" t="str">
+        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
+      <x:c r="C4" s="63"/>
+      <x:c r="D4" s="248"/>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="63"/>
+      <x:c r="G4" s="63"/>
+      <x:c r="H4" s="63"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -1821,6 +1673,10 @@
       <x:c r="F5"/>
       <x:c r="G5"/>
       <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="175" t="str">
@@ -1833,6 +1689,10 @@
       <x:c r="F6" s="175"/>
       <x:c r="G6" s="175"/>
       <x:c r="H6" s="175"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="181" t="str">
@@ -1842,7 +1702,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="C7" s="181" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>改訂内容</x:v>
       </x:c>
       <x:c r="D7" s="181" t="str">
         <x:v>作成者</x:v>
@@ -1859,6 +1719,10 @@
       <x:c r="H7" s="181" t="str">
         <x:v>備考</x:v>
       </x:c>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="67" t="str">
@@ -1880,11 +1744,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>基本設計初版</x:v>
       </x:c>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="67" t="str">
@@ -1906,11 +1774,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>Leader Review後Baseline化</x:v>
       </x:c>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="67" t="str">
@@ -1932,11 +1804,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>Review指摘対応</x:v>
       </x:c>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="67" t="str">
@@ -1958,11 +1834,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>再監査指摘対応</x:v>
       </x:c>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="67" t="str">
@@ -1984,11 +1864,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" s="67" t="str">
         <x:v>再監査第2回指摘対応</x:v>
       </x:c>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
@@ -2009,12 +1893,16 @@
       <x:c r="F13" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G13" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G13" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>再監査残項対応</x:v>
       </x:c>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -2035,12 +1923,16 @@
       <x:c r="F14" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G14" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G14" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>再Review指摘対応</x:v>
       </x:c>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
@@ -2061,25 +1953,187 @@
       <x:c r="F15" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G15" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G15" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>最大10回の反復監査対応</x:v>
+      </x:c>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>2.0</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>七項目Review指摘対応：画面・API・DB項目、論理削除、認証限流、日報関連Task、Baseline判定を整合</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>レビュー済</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Leader最終承認待ち</x:v>
+      </x:c>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>従業員・部門業務Review影響：退職入口、Excel取込結果、Data範囲を同期</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G17" s="203" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>第1回業務仕様Review指摘対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>従業員・部門業務仕様Review：詳細範囲・Import・部門状態/削除条件を整合</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G18" s="203" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>第2回業務仕様Review指摘対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="110" customHeight="1">
+      <x:c r="A19" s="241" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B19" s="241" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C19" s="241" t="str">
+        <x:v>内容・関連Reviewの既確定仕様を整合。業務未決事項は承認待ちとして管理。</x:v>
+      </x:c>
+      <x:c r="D19" s="241" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E19" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F19" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G19" s="241" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H19" s="241" t="str">
+        <x:v>2026-09-18指摘対応。正式承認を示すものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="40" customHeight="1">
+      <x:c r="A20" s="241" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B20" s="241" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C20" s="241" t="str">
+        <x:v>待確認12項目の方針選定、業務/API/DB/画面/運用を連動修正。章立て維持。</x:v>
+      </x:c>
+      <x:c r="D20" s="241" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E20" s="241" t="str">
+        <x:v>未実施</x:v>
+      </x:c>
+      <x:c r="F20" s="241" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G20" s="241" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H20" s="241" t="str">
+        <x:v>一般社内管理Systemの範囲。旧版はBackup保管。</x:v>
+      </x:c>
+      <x:c r="I20" s="241"/>
+      <x:c r="J20" s="241"/>
+      <x:c r="K20" s="241"/>
+      <x:c r="L20" s="241"/>
+    </x:row>
+    <x:row r="21" ht="100" customHeight="1">
+      <x:c r="A21" s="247" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B21" s="247" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="C21" s="247" t="str">
+        <x:v>共通規則・正本参照・構成・文書管理を統合修正。Baseline承認前の最終整合修正。</x:v>
+      </x:c>
+      <x:c r="D21" s="247" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E21" s="247" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F21" s="247" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G21" s="247" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H21" s="247" t="str">
+        <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2112,6 +2166,9 @@
       <x:c r="G1" s="68"/>
       <x:c r="H1" s="68"/>
       <x:c r="I1" s="68"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="68"/>
@@ -2123,44 +2180,45 @@
       <x:c r="G2" s="68"/>
       <x:c r="H2" s="68"/>
       <x:c r="I2" s="68"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="62" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="63" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B3" s="63" t="str"/>
       <x:c r="C3" s="63"/>
       <x:c r="D3" s="63"/>
-      <x:c r="E3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="63" t="str">
-        <x:v>CW-BD-API-ORG-LIST</x:v>
-      </x:c>
+      <x:c r="E3" s="248" t="str">
+        <x:v>章ID</x:v>
+      </x:c>
+      <x:c r="F3" s="63" t="str"/>
       <x:c r="G3" s="63"/>
       <x:c r="H3" s="63"/>
       <x:c r="I3" s="63"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
+      <x:c r="A4" s="248" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="63"/>
-      <x:c r="E4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="F4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
+      <x:c r="E4" s="248" t="str">
+        <x:v>改訂日：2026-09-24</x:v>
+      </x:c>
+      <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
       <x:c r="H4" s="63"/>
       <x:c r="I4" s="63"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="64"/>
@@ -2172,6 +2230,9 @@
       <x:c r="G5" s="64"/>
       <x:c r="H5" s="64"/>
       <x:c r="I5" s="64"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="65" t="str">
@@ -2185,6 +2246,9 @@
       <x:c r="G6" s="65"/>
       <x:c r="H6" s="65"/>
       <x:c r="I6" s="65"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="66" t="str">
@@ -2214,8 +2278,11 @@
       <x:c r="I7" s="66" t="str">
         <x:v>Error Code</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
+    </x:row>
+    <x:row r="8" ht="39" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-EMP-001</x:v>
       </x:c>
@@ -2229,22 +2296,25 @@
         <x:v>従業員ページ検索</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
-        <x:v>管理者/PM</x:v>
+        <x:v>02／13_API権限対応：API-EMP-001</x:v>
       </x:c>
       <x:c r="F8" s="67" t="str">
-        <x:v>query: employeeCode,name,email,departmentId,joinedFrom,joinedTo,status,page,size,sort</x:v>
+        <x:v>23_API項目定義：API-EMP-001 Request</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>Page&lt;EmployeeSummary&gt;</x:v>
+        <x:v>23_API項目定義：API-EMP-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>SCR-003</x:v>
       </x:c>
       <x:c r="I8" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F8／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+    </x:row>
+    <x:row r="9" ht="39" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-EMP-002</x:v>
       </x:c>
@@ -2258,22 +2328,25 @@
         <x:v>従業員詳細</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
-        <x:v>管理者/PM</x:v>
+        <x:v>02／13_API権限対応：API-EMP-002</x:v>
       </x:c>
       <x:c r="F9" s="67" t="str">
-        <x:v>path: id Long</x:v>
+        <x:v>23_API項目定義：API-EMP-002 Request</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>EmployeeDetail + projects[] + tasks[]</x:v>
+        <x:v>23_API項目定義：API-EMP-002 Response（正本）</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>SCR-005, SCR-006</x:v>
       </x:c>
       <x:c r="I9" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F9／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
+    </x:row>
+    <x:row r="10" ht="39" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-EMP-003</x:v>
       </x:c>
@@ -2287,22 +2360,25 @@
         <x:v>従業員登録</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-EMP-003</x:v>
       </x:c>
       <x:c r="F10" s="67" t="str">
-        <x:v>body: employeeCode,name,nameKana,email,phone,departmentId,position,joinedDate,managerId,username,roleIds,remark; header: X-Idempotency-Key</x:v>
+        <x:v>23_API項目定義：API-EMP-003 Request</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>id,employeeCode,temporaryPassword</x:v>
+        <x:v>23_API項目定義：API-EMP-003 Response（正本）</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>SCR-004</x:v>
       </x:c>
       <x:c r="I10" s="67" t="str">
-        <x:v>EMP-4001, EMP-4002, EMP-4003,COMMON-4000, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F10／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+    </x:row>
+    <x:row r="11" ht="39" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-EMP-004</x:v>
       </x:c>
@@ -2316,22 +2392,25 @@
         <x:v>従業員更新</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-EMP-004</x:v>
       </x:c>
       <x:c r="F11" s="67" t="str">
-        <x:v>path: id; body: name,nameKana,email,phone,departmentId,position,managerId,remark,version</x:v>
+        <x:v>23_API項目定義：API-EMP-004 Request</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>id,version</x:v>
+        <x:v>23_API項目定義：API-EMP-004 Response（正本）</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>SCR-005</x:v>
       </x:c>
       <x:c r="I11" s="67" t="str">
-        <x:v>EMP-4002,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F11／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+    </x:row>
+    <x:row r="12" ht="39" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-EMP-005</x:v>
       </x:c>
@@ -2345,22 +2424,25 @@
         <x:v>従業員状態変更</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-EMP-005</x:v>
       </x:c>
       <x:c r="F12" s="67" t="str">
-        <x:v>path: id; body: status,leftDate,unfinishedTaskPolicy,reassignmentAssigneeId,version</x:v>
+        <x:v>23_API項目定義：API-EMP-005 Request</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>id,status,version</x:v>
+        <x:v>23_API項目定義：API-EMP-005 Response（正本）</x:v>
       </x:c>
       <x:c r="H12" s="67" t="str">
-        <x:v>SCR-005, SCR-006</x:v>
+        <x:v>SCR-005</x:v>
       </x:c>
       <x:c r="I12" s="67" t="str">
-        <x:v>EMP-4004,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F12／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13" ht="39" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-EMP-006</x:v>
       </x:c>
@@ -2374,22 +2456,25 @@
         <x:v>従業員Excel取込</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-EMP-006</x:v>
       </x:c>
       <x:c r="F13" s="67" t="str">
-        <x:v>multipart: file xlsx &lt;=10MB; header: X-Idempotency-Key</x:v>
+        <x:v>23_API項目定義：API-EMP-006 Request</x:v>
       </x:c>
       <x:c r="G13" s="67" t="str">
-        <x:v>total,success,failed,errors[{row,field,code,message}]</x:v>
+        <x:v>23_API項目定義：API-EMP-006 Response（正本）</x:v>
       </x:c>
       <x:c r="H13" s="67" t="str">
         <x:v>SCR-003</x:v>
       </x:c>
       <x:c r="I13" s="67" t="str">
-        <x:v>FILE-4001, FILE-4002,EMP-4001, EMP-4002, EMP-4003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F13／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14" ht="39" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-EMP-007</x:v>
       </x:c>
@@ -2403,22 +2488,25 @@
         <x:v>従業員Excel出力</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-EMP-007</x:v>
       </x:c>
       <x:c r="F14" s="67" t="str">
-        <x:v>query: API-EMP-001と同一検索条件</x:v>
+        <x:v>23_API項目定義：API-EMP-007 Request</x:v>
       </x:c>
       <x:c r="G14" s="67" t="str">
-        <x:v>xlsx file</x:v>
+        <x:v>23_API項目定義：API-EMP-007 Response（正本）</x:v>
       </x:c>
       <x:c r="H14" s="67" t="str">
         <x:v>SCR-003</x:v>
       </x:c>
       <x:c r="I14" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F14／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15" ht="39" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-DEPT-001</x:v>
       </x:c>
@@ -2432,22 +2520,25 @@
         <x:v>部門Tree取得</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-DEPT-001</x:v>
       </x:c>
       <x:c r="F15" s="67" t="str">
-        <x:v>query: includeDisabled Boolean=false</x:v>
+        <x:v>23_API項目定義：API-DEPT-001 Request</x:v>
       </x:c>
       <x:c r="G15" s="67" t="str">
-        <x:v>DepartmentNode[]</x:v>
+        <x:v>23_API項目定義：API-DEPT-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H15" s="67" t="str">
         <x:v>SCR-007</x:v>
       </x:c>
       <x:c r="I15" s="67" t="str">
-        <x:v>COMMON-5000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F15／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16" ht="39" customHeight="1">
       <x:c r="A16" s="67" t="str">
         <x:v>API-DEPT-002</x:v>
       </x:c>
@@ -2461,22 +2552,25 @@
         <x:v>部門詳細</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-DEPT-002</x:v>
       </x:c>
       <x:c r="F16" s="67" t="str">
-        <x:v>path: id Long</x:v>
+        <x:v>23_API項目定義：API-DEPT-002 Request</x:v>
       </x:c>
       <x:c r="G16" s="67" t="str">
-        <x:v>id,code,name,parentId,managerId,displayOrder,status,version</x:v>
+        <x:v>23_API項目定義：API-DEPT-002 Response（正本）</x:v>
       </x:c>
       <x:c r="H16" s="67" t="str">
         <x:v>SCR-007</x:v>
       </x:c>
       <x:c r="I16" s="67" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F16／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="39" customHeight="1">
       <x:c r="A17" s="67" t="str">
         <x:v>API-DEPT-003</x:v>
       </x:c>
@@ -2490,22 +2584,25 @@
         <x:v>部門登録</x:v>
       </x:c>
       <x:c r="E17" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-DEPT-003</x:v>
       </x:c>
       <x:c r="F17" s="67" t="str">
-        <x:v>body: departmentCode,name,parentId,managerId,displayOrder,status; header: X-Idempotency-Key</x:v>
+        <x:v>23_API項目定義：API-DEPT-003 Request</x:v>
       </x:c>
       <x:c r="G17" s="67" t="str">
-        <x:v>id,version</x:v>
+        <x:v>23_API項目定義：API-DEPT-003 Response（正本）</x:v>
       </x:c>
       <x:c r="H17" s="67" t="str">
         <x:v>SCR-007</x:v>
       </x:c>
       <x:c r="I17" s="67" t="str">
-        <x:v>DEPT-4001, DEPT-4002,COMMON-4000, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F17／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
+    </x:row>
+    <x:row r="18" ht="39" customHeight="1">
       <x:c r="A18" s="67" t="str">
         <x:v>API-DEPT-004</x:v>
       </x:c>
@@ -2519,22 +2616,25 @@
         <x:v>部門更新</x:v>
       </x:c>
       <x:c r="E18" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-DEPT-004</x:v>
       </x:c>
       <x:c r="F18" s="67" t="str">
-        <x:v>path: id; body: name,parentId,managerId,displayOrder,status,version</x:v>
+        <x:v>23_API項目定義：API-DEPT-004 Request</x:v>
       </x:c>
       <x:c r="G18" s="67" t="str">
-        <x:v>id,version</x:v>
+        <x:v>23_API項目定義：API-DEPT-004 Response（正本）</x:v>
       </x:c>
       <x:c r="H18" s="67" t="str">
         <x:v>SCR-007</x:v>
       </x:c>
       <x:c r="I18" s="67" t="str">
-        <x:v>DEPT-4001, DEPT-4002,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F18／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
+    </x:row>
+    <x:row r="19" ht="39" customHeight="1">
       <x:c r="A19" s="67" t="str">
         <x:v>API-DEPT-005</x:v>
       </x:c>
@@ -2548,20 +2648,23 @@
         <x:v>部門削除</x:v>
       </x:c>
       <x:c r="E19" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-DEPT-005</x:v>
       </x:c>
       <x:c r="F19" s="67" t="str">
-        <x:v>path: id; query: version</x:v>
+        <x:v>23_API項目定義：API-DEPT-005 Request</x:v>
       </x:c>
       <x:c r="G19" s="67" t="str">
-        <x:v>204 No Content</x:v>
+        <x:v>23_API項目定義：API-DEPT-005 Response（正本）</x:v>
       </x:c>
       <x:c r="H19" s="67" t="str">
         <x:v>SCR-007</x:v>
       </x:c>
       <x:c r="I19" s="67" t="str">
-        <x:v>DEPT-4002, DEPT-4003,COMMON-4090</x:v>
-      </x:c>
+        <x:v>22_API処理・権限!F19／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20"/>
@@ -2573,6 +2676,9 @@
       <x:c r="G20"/>
       <x:c r="H20"/>
       <x:c r="I20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21"/>
@@ -2584,6 +2690,9 @@
       <x:c r="G21"/>
       <x:c r="H21"/>
       <x:c r="I21"/>
+      <x:c r="J21"/>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22"/>
@@ -2595,6 +2704,9 @@
       <x:c r="G22"/>
       <x:c r="H22"/>
       <x:c r="I22"/>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23"/>
@@ -2606,6 +2718,9 @@
       <x:c r="G23"/>
       <x:c r="H23"/>
       <x:c r="I23"/>
+      <x:c r="J23"/>
+      <x:c r="K23"/>
+      <x:c r="L23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24"/>
@@ -2617,6 +2732,9 @@
       <x:c r="G24"/>
       <x:c r="H24"/>
       <x:c r="I24"/>
+      <x:c r="J24"/>
+      <x:c r="K24"/>
+      <x:c r="L24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25"/>
@@ -2628,6 +2746,9 @@
       <x:c r="G25"/>
       <x:c r="H25"/>
       <x:c r="I25"/>
+      <x:c r="J25"/>
+      <x:c r="K25"/>
+      <x:c r="L25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26"/>
@@ -2639,6 +2760,9 @@
       <x:c r="G26"/>
       <x:c r="H26"/>
       <x:c r="I26"/>
+      <x:c r="J26"/>
+      <x:c r="K26"/>
+      <x:c r="L26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27"/>
@@ -2650,6 +2774,9 @@
       <x:c r="G27"/>
       <x:c r="H27"/>
       <x:c r="I27"/>
+      <x:c r="J27"/>
+      <x:c r="K27"/>
+      <x:c r="L27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28"/>
@@ -2661,6 +2788,9 @@
       <x:c r="G28"/>
       <x:c r="H28"/>
       <x:c r="I28"/>
+      <x:c r="J28"/>
+      <x:c r="K28"/>
+      <x:c r="L28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29"/>
@@ -2672,6 +2802,9 @@
       <x:c r="G29"/>
       <x:c r="H29"/>
       <x:c r="I29"/>
+      <x:c r="J29"/>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30"/>
@@ -2683,6 +2816,9 @@
       <x:c r="G30"/>
       <x:c r="H30"/>
       <x:c r="I30"/>
+      <x:c r="J30"/>
+      <x:c r="K30"/>
+      <x:c r="L30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31"/>
@@ -2694,6 +2830,9 @@
       <x:c r="G31"/>
       <x:c r="H31"/>
       <x:c r="I31"/>
+      <x:c r="J31"/>
+      <x:c r="K31"/>
+      <x:c r="L31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32"/>
@@ -2705,6 +2844,9 @@
       <x:c r="G32"/>
       <x:c r="H32"/>
       <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33"/>
@@ -2716,6 +2858,9 @@
       <x:c r="G33"/>
       <x:c r="H33"/>
       <x:c r="I33"/>
+      <x:c r="J33"/>
+      <x:c r="K33"/>
+      <x:c r="L33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34"/>
@@ -2727,6 +2872,9 @@
       <x:c r="G34"/>
       <x:c r="H34"/>
       <x:c r="I34"/>
+      <x:c r="J34"/>
+      <x:c r="K34"/>
+      <x:c r="L34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35"/>
@@ -2738,6 +2886,9 @@
       <x:c r="G35"/>
       <x:c r="H35"/>
       <x:c r="I35"/>
+      <x:c r="J35"/>
+      <x:c r="K35"/>
+      <x:c r="L35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36"/>
@@ -2749,6 +2900,9 @@
       <x:c r="G36"/>
       <x:c r="H36"/>
       <x:c r="I36"/>
+      <x:c r="J36"/>
+      <x:c r="K36"/>
+      <x:c r="L36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37"/>
@@ -2760,6 +2914,9 @@
       <x:c r="G37"/>
       <x:c r="H37"/>
       <x:c r="I37"/>
+      <x:c r="J37"/>
+      <x:c r="K37"/>
+      <x:c r="L37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38"/>
@@ -2771,6 +2928,9 @@
       <x:c r="G38"/>
       <x:c r="H38"/>
       <x:c r="I38"/>
+      <x:c r="J38"/>
+      <x:c r="K38"/>
+      <x:c r="L38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39"/>
@@ -2782,6 +2942,9 @@
       <x:c r="G39"/>
       <x:c r="H39"/>
       <x:c r="I39"/>
+      <x:c r="J39"/>
+      <x:c r="K39"/>
+      <x:c r="L39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40"/>
@@ -2793,6 +2956,9 @@
       <x:c r="G40"/>
       <x:c r="H40"/>
       <x:c r="I40"/>
+      <x:c r="J40"/>
+      <x:c r="K40"/>
+      <x:c r="L40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41"/>
@@ -2804,6 +2970,9 @@
       <x:c r="G41"/>
       <x:c r="H41"/>
       <x:c r="I41"/>
+      <x:c r="J41"/>
+      <x:c r="K41"/>
+      <x:c r="L41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42"/>
@@ -2815,6 +2984,9 @@
       <x:c r="G42"/>
       <x:c r="H42"/>
       <x:c r="I42"/>
+      <x:c r="J42"/>
+      <x:c r="K42"/>
+      <x:c r="L42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43"/>
@@ -2826,6 +2998,9 @@
       <x:c r="G43"/>
       <x:c r="H43"/>
       <x:c r="I43"/>
+      <x:c r="J43"/>
+      <x:c r="K43"/>
+      <x:c r="L43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44"/>
@@ -2837,6 +3012,9 @@
       <x:c r="G44"/>
       <x:c r="H44"/>
       <x:c r="I44"/>
+      <x:c r="J44"/>
+      <x:c r="K44"/>
+      <x:c r="L44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45"/>
@@ -2848,6 +3026,9 @@
       <x:c r="G45"/>
       <x:c r="H45"/>
       <x:c r="I45"/>
+      <x:c r="J45"/>
+      <x:c r="K45"/>
+      <x:c r="L45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46"/>
@@ -2859,6 +3040,9 @@
       <x:c r="G46"/>
       <x:c r="H46"/>
       <x:c r="I46"/>
+      <x:c r="J46"/>
+      <x:c r="K46"/>
+      <x:c r="L46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47"/>
@@ -2870,6 +3054,9 @@
       <x:c r="G47"/>
       <x:c r="H47"/>
       <x:c r="I47"/>
+      <x:c r="J47"/>
+      <x:c r="K47"/>
+      <x:c r="L47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48"/>
@@ -2881,6 +3068,9 @@
       <x:c r="G48"/>
       <x:c r="H48"/>
       <x:c r="I48"/>
+      <x:c r="J48"/>
+      <x:c r="K48"/>
+      <x:c r="L48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49"/>
@@ -2892,6 +3082,9 @@
       <x:c r="G49"/>
       <x:c r="H49"/>
       <x:c r="I49"/>
+      <x:c r="J49"/>
+      <x:c r="K49"/>
+      <x:c r="L49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50"/>
@@ -2903,6 +3096,9 @@
       <x:c r="G50"/>
       <x:c r="H50"/>
       <x:c r="I50"/>
+      <x:c r="J50"/>
+      <x:c r="K50"/>
+      <x:c r="L50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51"/>
@@ -2914,6 +3110,9 @@
       <x:c r="G51"/>
       <x:c r="H51"/>
       <x:c r="I51"/>
+      <x:c r="J51"/>
+      <x:c r="K51"/>
+      <x:c r="L51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52"/>
@@ -2925,6 +3124,9 @@
       <x:c r="G52"/>
       <x:c r="H52"/>
       <x:c r="I52"/>
+      <x:c r="J52"/>
+      <x:c r="K52"/>
+      <x:c r="L52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53"/>
@@ -2936,6 +3138,9 @@
       <x:c r="G53"/>
       <x:c r="H53"/>
       <x:c r="I53"/>
+      <x:c r="J53"/>
+      <x:c r="K53"/>
+      <x:c r="L53"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2958,490 +3163,463 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="68" t="str">
-        <x:v>API外部契約</x:v>
-      </x:c>
-      <x:c r="B1" s="68"/>
-      <x:c r="C1" s="68"/>
-      <x:c r="D1" s="68"/>
-      <x:c r="E1" s="68"/>
-      <x:c r="F1" s="68"/>
-      <x:c r="G1" s="68"/>
-      <x:c r="H1" s="68"/>
-      <x:c r="I1" s="68"/>
+      <x:c r="A1" s="252" t="str">
+        <x:v>21_エラーコード</x:v>
+      </x:c>
+      <x:c r="B1" s="251"/>
+      <x:c r="C1" s="251"/>
+      <x:c r="D1" s="251"/>
+      <x:c r="E1" s="251"/>
+      <x:c r="F1" s="251"/>
+      <x:c r="G1" s="251"/>
+      <x:c r="H1" s="251"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="68"/>
-      <x:c r="B2" s="68"/>
-      <x:c r="C2" s="68"/>
-      <x:c r="D2" s="68"/>
-      <x:c r="E2" s="68"/>
-      <x:c r="F2" s="68"/>
-      <x:c r="G2" s="68"/>
-      <x:c r="H2" s="68"/>
-      <x:c r="I2" s="68"/>
+      <x:c r="A2" s="251"/>
+      <x:c r="B2" s="251"/>
+      <x:c r="C2" s="251"/>
+      <x:c r="D2" s="251"/>
+      <x:c r="E2" s="251"/>
+      <x:c r="F2" s="251"/>
+      <x:c r="G2" s="251"/>
+      <x:c r="H2" s="251"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="62" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="63" t="str">
+      <x:c r="A3" s="251" t="str">
         <x:v>Company WorkHub</x:v>
       </x:c>
-      <x:c r="C3" s="63"/>
-      <x:c r="D3" s="63"/>
-      <x:c r="E3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="63" t="str">
-        <x:v>CW-BD-API-ORG-CONTRACT</x:v>
-      </x:c>
-      <x:c r="G3" s="63"/>
-      <x:c r="H3" s="63"/>
-      <x:c r="I3" s="63"/>
+      <x:c r="B3" s="251"/>
+      <x:c r="C3" s="251"/>
+      <x:c r="D3" s="251"/>
+      <x:c r="E3" s="251"/>
+      <x:c r="F3" s="251"/>
+      <x:c r="G3" s="251"/>
+      <x:c r="H3" s="251"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="63"/>
-      <x:c r="D4" s="63"/>
-      <x:c r="E4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="F4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="G4" s="63"/>
-      <x:c r="H4" s="63"/>
-      <x:c r="I4" s="63"/>
+      <x:c r="A4" s="251"/>
+      <x:c r="B4" s="251"/>
+      <x:c r="C4" s="251"/>
+      <x:c r="D4" s="251"/>
+      <x:c r="E4" s="251"/>
+      <x:c r="F4" s="251"/>
+      <x:c r="G4" s="251"/>
+      <x:c r="H4" s="251"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="64"/>
-      <x:c r="B5" s="64"/>
-      <x:c r="C5" s="64"/>
-      <x:c r="D5" s="64"/>
-      <x:c r="E5" s="64"/>
-      <x:c r="F5" s="64"/>
-      <x:c r="G5" s="64"/>
-      <x:c r="H5" s="64"/>
-      <x:c r="I5" s="64"/>
+      <x:c r="A5" s="251" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="251"/>
+      <x:c r="C5" s="251"/>
+      <x:c r="D5" s="251"/>
+      <x:c r="E5" s="251"/>
+      <x:c r="F5" s="251"/>
+      <x:c r="G5" s="251"/>
+      <x:c r="H5" s="251"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="65" t="str">
-        <x:v>1. 従業員・部門 Request/Response・権限契約</x:v>
-      </x:c>
-      <x:c r="B6" s="65"/>
-      <x:c r="C6" s="65"/>
-      <x:c r="D6" s="65"/>
-      <x:c r="E6" s="65"/>
-      <x:c r="F6" s="65"/>
-      <x:c r="G6" s="65"/>
-      <x:c r="H6" s="65"/>
-      <x:c r="I6" s="65"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="66" t="str">
-        <x:v>API ID</x:v>
-      </x:c>
-      <x:c r="B7" s="66" t="str">
-        <x:v>Request定義</x:v>
-      </x:c>
-      <x:c r="C7" s="66" t="str">
-        <x:v>Response定義</x:v>
-      </x:c>
-      <x:c r="D7" s="66" t="str">
-        <x:v>Role</x:v>
-      </x:c>
-      <x:c r="E7" s="66" t="str">
-        <x:v>Data範囲</x:v>
-      </x:c>
-      <x:c r="F7" s="66" t="str">
-        <x:v>参照・更新Table</x:v>
-      </x:c>
-      <x:c r="G7" s="66" t="str">
-        <x:v>Transaction</x:v>
-      </x:c>
-      <x:c r="H7" s="66" t="str">
+      <x:c r="A6" s="251"/>
+      <x:c r="B6" s="251"/>
+      <x:c r="C6" s="251"/>
+      <x:c r="D6" s="251"/>
+      <x:c r="E6" s="251"/>
+      <x:c r="F6" s="251"/>
+      <x:c r="G6" s="251"/>
+      <x:c r="H6" s="251"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="254" t="str">
         <x:v>Error Code</x:v>
       </x:c>
-      <x:c r="I7" s="66" t="str">
-        <x:v>利用画面</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="67" t="str">
-        <x:v>API-EMP-001</x:v>
-      </x:c>
-      <x:c r="B8" s="67" t="str">
-        <x:v>query: employeeCode,name,email,departmentId,joinedFrom,joinedTo,status,page,size,sort</x:v>
-      </x:c>
-      <x:c r="C8" s="67" t="str">
-        <x:v>Page&lt;EmployeeSummary&gt;</x:v>
-      </x:c>
-      <x:c r="D8" s="67" t="str">
-        <x:v>管理者/PM</x:v>
-      </x:c>
-      <x:c r="E8" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ関係社員</x:v>
-      </x:c>
-      <x:c r="F8" s="67" t="str">
-        <x:v>employees,departments,users,project_members</x:v>
-      </x:c>
-      <x:c r="G8" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H8" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="I8" s="67" t="str">
-        <x:v>SCR-003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="67" t="str">
-        <x:v>API-EMP-002</x:v>
-      </x:c>
-      <x:c r="B9" s="67" t="str">
-        <x:v>path: id Long</x:v>
-      </x:c>
-      <x:c r="C9" s="67" t="str">
-        <x:v>EmployeeDetail + projects[] + tasks[]</x:v>
-      </x:c>
-      <x:c r="D9" s="67" t="str">
-        <x:v>管理者/PM</x:v>
-      </x:c>
-      <x:c r="E9" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ関係社員</x:v>
-      </x:c>
-      <x:c r="F9" s="67" t="str">
-        <x:v>employees,departments,projects,tasks</x:v>
-      </x:c>
-      <x:c r="G9" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H9" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I9" s="67" t="str">
-        <x:v>SCR-005, SCR-006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="67" t="str">
-        <x:v>API-EMP-003</x:v>
-      </x:c>
-      <x:c r="B10" s="67" t="str">
-        <x:v>body: employeeCode,name,nameKana,email,phone,departmentId,position,joinedDate,managerId,username,roleIds,remark; header: X-Idempotency-Key</x:v>
-      </x:c>
-      <x:c r="C10" s="67" t="str">
-        <x:v>id,employeeCode,temporaryPassword</x:v>
-      </x:c>
-      <x:c r="D10" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E10" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F10" s="67" t="str">
-        <x:v>employees,users,user_roles,operation_logs</x:v>
-      </x:c>
-      <x:c r="G10" s="67" t="str">
-        <x:v>TX-001</x:v>
-      </x:c>
-      <x:c r="H10" s="67" t="str">
-        <x:v>EMP-4001, EMP-4002, EMP-4003,COMMON-4000, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I10" s="67" t="str">
-        <x:v>SCR-004</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="67" t="str">
-        <x:v>API-EMP-004</x:v>
-      </x:c>
-      <x:c r="B11" s="67" t="str">
-        <x:v>path: id; body: name,nameKana,email,phone,departmentId,position,managerId,remark,version</x:v>
-      </x:c>
-      <x:c r="C11" s="67" t="str">
-        <x:v>id,version</x:v>
-      </x:c>
-      <x:c r="D11" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E11" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F11" s="67" t="str">
-        <x:v>employees,operation_logs</x:v>
-      </x:c>
-      <x:c r="G11" s="67" t="str">
-        <x:v>TX-015</x:v>
-      </x:c>
-      <x:c r="H11" s="67" t="str">
-        <x:v>EMP-4002,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I11" s="67" t="str">
-        <x:v>SCR-005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="67" t="str">
-        <x:v>API-EMP-005</x:v>
-      </x:c>
-      <x:c r="B12" s="67" t="str">
-        <x:v>path: id; body: status,leftDate,unfinishedTaskPolicy,reassignmentAssigneeId,version</x:v>
-      </x:c>
-      <x:c r="C12" s="67" t="str">
-        <x:v>id,status,version</x:v>
-      </x:c>
-      <x:c r="D12" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E12" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F12" s="67" t="str">
-        <x:v>employees,users,tasks,refresh_tokens / Redis</x:v>
-      </x:c>
-      <x:c r="G12" s="67" t="str">
-        <x:v>TX-005</x:v>
-      </x:c>
-      <x:c r="H12" s="67" t="str">
-        <x:v>EMP-4004,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I12" s="67" t="str">
-        <x:v>SCR-005, SCR-006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="67" t="str">
-        <x:v>API-EMP-006</x:v>
-      </x:c>
-      <x:c r="B13" s="67" t="str">
-        <x:v>multipart: file xlsx &lt;=10MB; header: X-Idempotency-Key</x:v>
-      </x:c>
-      <x:c r="C13" s="67" t="str">
-        <x:v>total,success,failed,errors[{row,field,code,message}]</x:v>
-      </x:c>
-      <x:c r="D13" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E13" s="67" t="str">
-        <x:v>管理者のみ; 行単位検証・行単位Transaction。成功行のみCommitし、失敗行はRollbackしてError明細返却</x:v>
-      </x:c>
-      <x:c r="F13" s="67" t="str">
-        <x:v>employees,users,user_roles,operation_logs</x:v>
-      </x:c>
-      <x:c r="G13" s="67" t="str">
-        <x:v>TX-016</x:v>
-      </x:c>
-      <x:c r="H13" s="67" t="str">
-        <x:v>FILE-4001, FILE-4002,EMP-4001, EMP-4002, EMP-4003</x:v>
-      </x:c>
-      <x:c r="I13" s="67" t="str">
-        <x:v>SCR-003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="67" t="str">
-        <x:v>API-EMP-007</x:v>
-      </x:c>
-      <x:c r="B14" s="67" t="str">
-        <x:v>query: API-EMP-001と同一検索条件</x:v>
-      </x:c>
-      <x:c r="C14" s="67" t="str">
-        <x:v>xlsx file</x:v>
-      </x:c>
-      <x:c r="D14" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E14" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F14" s="67" t="str">
-        <x:v>employees,departments,users,roles</x:v>
-      </x:c>
-      <x:c r="G14" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H14" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="I14" s="67" t="str">
-        <x:v>SCR-003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="67" t="str">
-        <x:v>API-DEPT-001</x:v>
-      </x:c>
-      <x:c r="B15" s="67" t="str">
-        <x:v>query: includeDisabled Boolean=false</x:v>
-      </x:c>
-      <x:c r="C15" s="67" t="str">
-        <x:v>DepartmentNode[]</x:v>
-      </x:c>
-      <x:c r="D15" s="67" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E15" s="67" t="str">
-        <x:v>一般=有効部門, 管理者=指定可</x:v>
-      </x:c>
-      <x:c r="F15" s="67" t="str">
-        <x:v>departments / Redis</x:v>
-      </x:c>
-      <x:c r="G15" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H15" s="67" t="str">
-        <x:v>COMMON-5000</x:v>
-      </x:c>
-      <x:c r="I15" s="67" t="str">
-        <x:v>SCR-007</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="67" t="str">
-        <x:v>API-DEPT-002</x:v>
-      </x:c>
-      <x:c r="B16" s="67" t="str">
-        <x:v>path: id Long</x:v>
-      </x:c>
-      <x:c r="C16" s="67" t="str">
-        <x:v>id,code,name,parentId,managerId,displayOrder,status,version</x:v>
-      </x:c>
-      <x:c r="D16" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E16" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F16" s="67" t="str">
-        <x:v>departments,employees</x:v>
-      </x:c>
-      <x:c r="G16" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H16" s="67" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-      <x:c r="I16" s="67" t="str">
-        <x:v>SCR-007</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="67" t="str">
-        <x:v>API-DEPT-003</x:v>
-      </x:c>
-      <x:c r="B17" s="67" t="str">
-        <x:v>body: departmentCode,name,parentId,managerId,displayOrder,status; header: X-Idempotency-Key</x:v>
-      </x:c>
-      <x:c r="C17" s="67" t="str">
-        <x:v>id,version</x:v>
-      </x:c>
-      <x:c r="D17" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E17" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F17" s="67" t="str">
-        <x:v>departments,operation_logs / Redis</x:v>
-      </x:c>
-      <x:c r="G17" s="67" t="str">
-        <x:v>TX-017</x:v>
-      </x:c>
-      <x:c r="H17" s="67" t="str">
-        <x:v>DEPT-4001, DEPT-4002,COMMON-4000, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I17" s="67" t="str">
-        <x:v>SCR-007</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="67" t="str">
-        <x:v>API-DEPT-004</x:v>
-      </x:c>
-      <x:c r="B18" s="67" t="str">
-        <x:v>path: id; body: name,parentId,managerId,displayOrder,status,version</x:v>
-      </x:c>
-      <x:c r="C18" s="67" t="str">
-        <x:v>id,version</x:v>
-      </x:c>
-      <x:c r="D18" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E18" s="67" t="str">
-        <x:v>自己・子孫を親に設定不可</x:v>
-      </x:c>
-      <x:c r="F18" s="67" t="str">
-        <x:v>departments,operation_logs / Redis</x:v>
-      </x:c>
-      <x:c r="G18" s="67" t="str">
-        <x:v>TX-017</x:v>
-      </x:c>
-      <x:c r="H18" s="67" t="str">
-        <x:v>DEPT-4001, DEPT-4002,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I18" s="67" t="str">
-        <x:v>SCR-007</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="30" customHeight="1">
-      <x:c r="A19" s="67" t="str">
-        <x:v>API-DEPT-005</x:v>
-      </x:c>
-      <x:c r="B19" s="67" t="str">
-        <x:v>path: id; query: version</x:v>
-      </x:c>
-      <x:c r="C19" s="67" t="str">
-        <x:v>204 No Content</x:v>
-      </x:c>
-      <x:c r="D19" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E19" s="67" t="str">
-        <x:v>社員・子部門・PJ関連なし</x:v>
-      </x:c>
-      <x:c r="F19" s="67" t="str">
-        <x:v>departments,employees,projects / Redis</x:v>
-      </x:c>
-      <x:c r="G19" s="67" t="str">
-        <x:v>TX-017</x:v>
-      </x:c>
-      <x:c r="H19" s="67" t="str">
-        <x:v>DEPT-4002, DEPT-4003,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I19" s="67" t="str">
-        <x:v>SCR-007</x:v>
-      </x:c>
+      <x:c r="B7" s="254" t="str">
+        <x:v>分類</x:v>
+      </x:c>
+      <x:c r="C7" s="254" t="str">
+        <x:v>業務上の意味</x:v>
+      </x:c>
+      <x:c r="D7" s="254" t="str">
+        <x:v>HTTP Status</x:v>
+      </x:c>
+      <x:c r="E7" s="254" t="str">
+        <x:v>Message参照</x:v>
+      </x:c>
+      <x:c r="F7" s="254" t="str">
+        <x:v>Log Level</x:v>
+      </x:c>
+      <x:c r="G7" s="254" t="str">
+        <x:v>再試行</x:v>
+      </x:c>
+      <x:c r="H7" s="254" t="str">
+        <x:v>備考</x:v>
+      </x:c>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="256" t="str">
+        <x:v>EMP-4001</x:v>
+      </x:c>
+      <x:c r="B8" s="256" t="str">
+        <x:v>社員</x:v>
+      </x:c>
+      <x:c r="C8" s="256" t="str">
+        <x:v>社員番号重複</x:v>
+      </x:c>
+      <x:c r="D8" s="256" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="E8" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F8" s="256" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G8" s="256" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H8" s="256" t="str"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="255" t="str">
+        <x:v>EMP-4002</x:v>
+      </x:c>
+      <x:c r="B9" s="255" t="str">
+        <x:v>社員</x:v>
+      </x:c>
+      <x:c r="C9" s="255" t="str">
+        <x:v>Email重複</x:v>
+      </x:c>
+      <x:c r="D9" s="255" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="E9" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F9" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G9" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H9" s="255" t="str"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="256" t="str">
+        <x:v>EMP-4003</x:v>
+      </x:c>
+      <x:c r="B10" s="256" t="str">
+        <x:v>社員</x:v>
+      </x:c>
+      <x:c r="C10" s="256" t="str">
+        <x:v>User名重複</x:v>
+      </x:c>
+      <x:c r="D10" s="256" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="E10" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F10" s="256" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G10" s="256" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H10" s="256" t="str"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="255" t="str">
+        <x:v>EMP-4004</x:v>
+      </x:c>
+      <x:c r="B11" s="255" t="str">
+        <x:v>社員</x:v>
+      </x:c>
+      <x:c r="C11" s="255" t="str">
+        <x:v>社員存在しない</x:v>
+      </x:c>
+      <x:c r="D11" s="255" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="E11" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F11" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G11" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H11" s="255" t="str"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="256" t="str">
+        <x:v>DEPT-4001</x:v>
+      </x:c>
+      <x:c r="B12" s="256" t="str">
+        <x:v>部門</x:v>
+      </x:c>
+      <x:c r="C12" s="256" t="str">
+        <x:v>部門番号または同一階層部門名重複</x:v>
+      </x:c>
+      <x:c r="D12" s="256" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="E12" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F12" s="256" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G12" s="256" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H12" s="256" t="str"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="255" t="str">
+        <x:v>DEPT-4002</x:v>
+      </x:c>
+      <x:c r="B13" s="255" t="str">
+        <x:v>部門</x:v>
+      </x:c>
+      <x:c r="C13" s="255" t="str">
+        <x:v>子部門あり</x:v>
+      </x:c>
+      <x:c r="D13" s="255" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E13" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F13" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G13" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H13" s="255" t="str"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="256" t="str">
+        <x:v>DEPT-4003</x:v>
+      </x:c>
+      <x:c r="B14" s="256" t="str">
+        <x:v>部門</x:v>
+      </x:c>
+      <x:c r="C14" s="256" t="str">
+        <x:v>社員あり</x:v>
+      </x:c>
+      <x:c r="D14" s="256" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E14" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F14" s="256" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G14" s="256" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H14" s="256" t="str"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="255" t="str">
+        <x:v>EMP-4005</x:v>
+      </x:c>
+      <x:c r="B15" s="255" t="str">
+        <x:v>社員</x:v>
+      </x:c>
+      <x:c r="C15" s="255" t="str">
+        <x:v>在籍状態遷移不正</x:v>
+      </x:c>
+      <x:c r="D15" s="255" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E15" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F15" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G15" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H15" s="255" t="str">
+        <x:v>EMPLOYED→LEFTのみ</x:v>
+      </x:c>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="256" t="str">
+        <x:v>EMP-4006</x:v>
+      </x:c>
+      <x:c r="B16" s="256" t="str">
+        <x:v>社員</x:v>
+      </x:c>
+      <x:c r="C16" s="256" t="str">
+        <x:v>上司または退職引継先不正</x:v>
+      </x:c>
+      <x:c r="D16" s="256" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E16" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F16" s="256" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G16" s="256" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H16" s="256" t="str">
+        <x:v>在籍・本人以外・PJ Member条件</x:v>
+      </x:c>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="255" t="str">
+        <x:v>EMP-4007</x:v>
+      </x:c>
+      <x:c r="B17" s="255" t="str">
+        <x:v>社員</x:v>
+      </x:c>
+      <x:c r="C17" s="255" t="str">
+        <x:v>担当中PJのPM</x:v>
+      </x:c>
+      <x:c r="D17" s="255" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E17" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F17" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G17" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H17" s="255" t="str">
+        <x:v>先にPM変更</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="256" t="str">
+        <x:v>DEPT-4004</x:v>
+      </x:c>
+      <x:c r="B18" s="256" t="str">
+        <x:v>部門</x:v>
+      </x:c>
+      <x:c r="C18" s="256" t="str">
+        <x:v>Rootまたは停止条件不成立</x:v>
+      </x:c>
+      <x:c r="D18" s="256" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E18" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F18" s="256" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G18" s="256" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H18" s="256" t="str">
+        <x:v>Root/在籍社員/子部門</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="64"/>
-      <x:c r="B20" s="64"/>
-      <x:c r="C20" s="64"/>
-      <x:c r="D20" s="64"/>
-      <x:c r="E20" s="64"/>
-      <x:c r="F20" s="64"/>
-      <x:c r="G20" s="64"/>
-      <x:c r="H20" s="64"/>
-      <x:c r="I20" s="64"/>
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21"/>
@@ -3452,18 +3630,16 @@
       <x:c r="F21"/>
       <x:c r="G21"/>
       <x:c r="H21"/>
-      <x:c r="I21"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="91"/>
-      <x:c r="B22" s="92"/>
-      <x:c r="C22" s="92"/>
-      <x:c r="D22" s="92"/>
-      <x:c r="E22" s="92"/>
-      <x:c r="F22" s="92"/>
-      <x:c r="G22" s="92"/>
-      <x:c r="H22" s="92"/>
-      <x:c r="I22" s="93"/>
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23"/>
@@ -3474,7 +3650,6 @@
       <x:c r="F23"/>
       <x:c r="G23"/>
       <x:c r="H23"/>
-      <x:c r="I23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24"/>
@@ -3485,7 +3660,6 @@
       <x:c r="F24"/>
       <x:c r="G24"/>
       <x:c r="H24"/>
-      <x:c r="I24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25"/>
@@ -3496,7 +3670,6 @@
       <x:c r="F25"/>
       <x:c r="G25"/>
       <x:c r="H25"/>
-      <x:c r="I25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26"/>
@@ -3507,7 +3680,6 @@
       <x:c r="F26"/>
       <x:c r="G26"/>
       <x:c r="H26"/>
-      <x:c r="I26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27"/>
@@ -3518,7 +3690,6 @@
       <x:c r="F27"/>
       <x:c r="G27"/>
       <x:c r="H27"/>
-      <x:c r="I27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28"/>
@@ -3529,21 +3700,102 @@
       <x:c r="F28"/>
       <x:c r="G28"/>
       <x:c r="H28"/>
-      <x:c r="I28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
+      <x:c r="H35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+      <x:c r="G36"/>
+      <x:c r="H36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+      <x:c r="H37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:I2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:I3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:I4"/>
-    <x:mergeCell ref="A6:I6"/>
-    <x:mergeCell ref="A21:I22"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3554,607 +3806,14 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="50" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="20" t="str">
-        <x:v>業務エラーコード</x:v>
-      </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
-      <x:c r="H1" s="20"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="20"/>
-      <x:c r="B2" s="20"/>
-      <x:c r="C2" s="20"/>
-      <x:c r="D2" s="20"/>
-      <x:c r="E2" s="20"/>
-      <x:c r="F2" s="20"/>
-      <x:c r="G2" s="20"/>
-      <x:c r="H2" s="20"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="23" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="23"/>
-      <x:c r="C3" s="21" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="23"/>
-      <x:c r="G3" s="21" t="str">
-        <x:v>CW-BD-053</x:v>
-      </x:c>
-      <x:c r="H3" s="21"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="D4" s="21"/>
-      <x:c r="E4" s="23" t="str">
-        <x:v>作成日</x:v>
-      </x:c>
-      <x:c r="F4" s="23"/>
-      <x:c r="G4" s="24" t="n">
-        <x:v>46239</x:v>
-      </x:c>
-      <x:c r="H4" s="24"/>
-    </x:row>
-    <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="26" t="str">
-        <x:v>1. Error Code</x:v>
-      </x:c>
-      <x:c r="B6" s="26"/>
-      <x:c r="C6" s="26"/>
-      <x:c r="D6" s="26"/>
-      <x:c r="E6" s="26"/>
-      <x:c r="F6" s="26"/>
-      <x:c r="G6" s="26"/>
-      <x:c r="H6" s="26"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="31" t="str">
-        <x:v>Error Code</x:v>
-      </x:c>
-      <x:c r="B7" s="31" t="str">
-        <x:v>分類</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="str">
-        <x:v>意味</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="str">
-        <x:v>HTTP Status</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="str">
-        <x:v>画面Message</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="str">
-        <x:v>記録Level</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="str">
-        <x:v>再試行</x:v>
-      </x:c>
-      <x:c r="H7" s="31" t="str">
-        <x:v>備考</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>COMMON-0000</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>成功</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
-        <x:v>処理成功</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="str">
-        <x:v>処理成功</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="str">
-        <x:v>INFO</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H8" s="33"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>入力</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
-        <x:v>Request parameter error</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E9" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H9" s="33"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>Data</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
-        <x:v>Data存在しない</x:v>
-      </x:c>
-      <x:c r="D10" s="33" t="n">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="E10" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F10" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G10" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H10" s="33"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>COMMON-4090</x:v>
-      </x:c>
-      <x:c r="B11" s="33" t="str">
-        <x:v>競合</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="str">
-        <x:v>並行更新Conflict</x:v>
-      </x:c>
-      <x:c r="D11" s="33" t="n">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="E11" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F11" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G11" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H11" s="33"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>COMMON-5000</x:v>
-      </x:c>
-      <x:c r="B12" s="33" t="str">
-        <x:v>System</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="str">
-        <x:v>System error</x:v>
-      </x:c>
-      <x:c r="D12" s="33" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="E12" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F12" s="33" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="G12" s="33" t="str">
-        <x:v>可</x:v>
-      </x:c>
-      <x:c r="H12" s="33"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>EMP-4001</x:v>
-      </x:c>
-      <x:c r="B13" s="33" t="str">
-        <x:v>社員</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="str">
-        <x:v>社員番号重複</x:v>
-      </x:c>
-      <x:c r="D13" s="33" t="n">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="E13" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F13" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G13" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H13" s="33"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="33" t="str">
-        <x:v>EMP-4002</x:v>
-      </x:c>
-      <x:c r="B14" s="33" t="str">
-        <x:v>社員</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="str">
-        <x:v>Email重複</x:v>
-      </x:c>
-      <x:c r="D14" s="33" t="n">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="E14" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F14" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G14" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H14" s="33"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="33" t="str">
-        <x:v>EMP-4003</x:v>
-      </x:c>
-      <x:c r="B15" s="33" t="str">
-        <x:v>社員</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="str">
-        <x:v>User名重複</x:v>
-      </x:c>
-      <x:c r="D15" s="33" t="n">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="E15" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F15" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G15" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H15" s="33"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="33" t="str">
-        <x:v>EMP-4004</x:v>
-      </x:c>
-      <x:c r="B16" s="33" t="str">
-        <x:v>社員</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="str">
-        <x:v>社員存在しない</x:v>
-      </x:c>
-      <x:c r="D16" s="33" t="n">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="E16" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F16" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G16" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H16" s="33"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="33" t="str">
-        <x:v>DEPT-4001</x:v>
-      </x:c>
-      <x:c r="B17" s="33" t="str">
-        <x:v>部門</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="str">
-        <x:v>部門番号重複</x:v>
-      </x:c>
-      <x:c r="D17" s="33" t="n">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="E17" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F17" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G17" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H17" s="33"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="33" t="str">
-        <x:v>DEPT-4002</x:v>
-      </x:c>
-      <x:c r="B18" s="33" t="str">
-        <x:v>部門</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="str">
-        <x:v>子部門あり</x:v>
-      </x:c>
-      <x:c r="D18" s="33" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E18" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F18" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G18" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H18" s="33"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="33" t="str">
-        <x:v>DEPT-4003</x:v>
-      </x:c>
-      <x:c r="B19" s="33" t="str">
-        <x:v>部門</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="str">
-        <x:v>社員あり</x:v>
-      </x:c>
-      <x:c r="D19" s="33" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E19" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F19" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G19" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H19" s="33"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20"/>
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
-      <x:c r="G21"/>
-      <x:c r="H21"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22"/>
-      <x:c r="B22"/>
-      <x:c r="C22"/>
-      <x:c r="D22"/>
-      <x:c r="E22"/>
-      <x:c r="F22"/>
-      <x:c r="G22"/>
-      <x:c r="H22"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23"/>
-      <x:c r="C23"/>
-      <x:c r="D23"/>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
-      <x:c r="G23"/>
-      <x:c r="H23"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24"/>
-      <x:c r="B24"/>
-      <x:c r="C24"/>
-      <x:c r="D24"/>
-      <x:c r="E24"/>
-      <x:c r="F24"/>
-      <x:c r="G24"/>
-      <x:c r="H24"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25"/>
-      <x:c r="B25"/>
-      <x:c r="C25"/>
-      <x:c r="D25"/>
-      <x:c r="E25"/>
-      <x:c r="F25"/>
-      <x:c r="G25"/>
-      <x:c r="H25"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26"/>
-      <x:c r="B26"/>
-      <x:c r="C26"/>
-      <x:c r="D26"/>
-      <x:c r="E26"/>
-      <x:c r="F26"/>
-      <x:c r="G26"/>
-      <x:c r="H26"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27"/>
-      <x:c r="B27"/>
-      <x:c r="C27"/>
-      <x:c r="D27"/>
-      <x:c r="E27"/>
-      <x:c r="F27"/>
-      <x:c r="G27"/>
-      <x:c r="H27"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28"/>
-      <x:c r="B28"/>
-      <x:c r="C28"/>
-      <x:c r="D28"/>
-      <x:c r="E28"/>
-      <x:c r="F28"/>
-      <x:c r="G28"/>
-      <x:c r="H28"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29"/>
-      <x:c r="B29"/>
-      <x:c r="C29"/>
-      <x:c r="D29"/>
-      <x:c r="E29"/>
-      <x:c r="F29"/>
-      <x:c r="G29"/>
-      <x:c r="H29"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30"/>
-      <x:c r="B30"/>
-      <x:c r="C30"/>
-      <x:c r="D30"/>
-      <x:c r="E30"/>
-      <x:c r="F30"/>
-      <x:c r="G30"/>
-      <x:c r="H30"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31"/>
-      <x:c r="B31"/>
-      <x:c r="C31"/>
-      <x:c r="D31"/>
-      <x:c r="E31"/>
-      <x:c r="F31"/>
-      <x:c r="G31"/>
-      <x:c r="H31"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32"/>
-      <x:c r="B32"/>
-      <x:c r="C32"/>
-      <x:c r="D32"/>
-      <x:c r="E32"/>
-      <x:c r="F32"/>
-      <x:c r="G32"/>
-      <x:c r="H32"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33"/>
-      <x:c r="B33"/>
-      <x:c r="C33"/>
-      <x:c r="D33"/>
-      <x:c r="E33"/>
-      <x:c r="F33"/>
-      <x:c r="G33"/>
-      <x:c r="H33"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34"/>
-      <x:c r="B34"/>
-      <x:c r="C34"/>
-      <x:c r="D34"/>
-      <x:c r="E34"/>
-      <x:c r="F34"/>
-      <x:c r="G34"/>
-      <x:c r="H34"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35"/>
-      <x:c r="B35"/>
-      <x:c r="C35"/>
-      <x:c r="D35"/>
-      <x:c r="E35"/>
-      <x:c r="F35"/>
-      <x:c r="G35"/>
-      <x:c r="H35"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36"/>
-      <x:c r="B36"/>
-      <x:c r="C36"/>
-      <x:c r="D36"/>
-      <x:c r="E36"/>
-      <x:c r="F36"/>
-      <x:c r="G36"/>
-      <x:c r="H36"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37"/>
-      <x:c r="B37"/>
-      <x:c r="C37"/>
-      <x:c r="D37"/>
-      <x:c r="E37"/>
-      <x:c r="F37"/>
-      <x:c r="G37"/>
-      <x:c r="H37"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
-    <x:mergeCell ref="A6:H6"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="90" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="44" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -4167,6 +3826,11 @@
       <x:c r="E1" s="68"/>
       <x:c r="F1" s="68"/>
       <x:c r="G1" s="68"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="68"/>
@@ -4176,6 +3840,11 @@
       <x:c r="E2" s="68"/>
       <x:c r="F2" s="68"/>
       <x:c r="G2" s="68"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="62" t="str">
@@ -4185,31 +3854,41 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="63"/>
-      <x:c r="D3" s="62" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="D3" s="248" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="E3" s="63" t="str">
         <x:v>CW-BD-API-ORG-FLOW</x:v>
       </x:c>
       <x:c r="F3" s="63"/>
       <x:c r="G3" s="63"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="62" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="62" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="64"/>
@@ -4219,6 +3898,11 @@
       <x:c r="E5" s="64"/>
       <x:c r="F5" s="64"/>
       <x:c r="G5" s="64"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="65" t="str">
@@ -4230,6 +3914,11 @@
       <x:c r="E6" s="65"/>
       <x:c r="F6" s="65"/>
       <x:c r="G6" s="65"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="66" t="str">
@@ -4241,8 +3930,8 @@
       <x:c r="C7" s="66" t="str">
         <x:v>処理概要</x:v>
       </x:c>
-      <x:c r="D7" s="66" t="str">
-        <x:v>Data範囲</x:v>
+      <x:c r="D7" s="257" t="str">
+        <x:v>認可参照</x:v>
       </x:c>
       <x:c r="E7" s="66" t="str">
         <x:v>Transaction</x:v>
@@ -4253,6 +3942,15 @@
       <x:c r="G7" s="66" t="str">
         <x:v>Log</x:v>
       </x:c>
+      <x:c r="H7" s="203" t="str">
+        <x:v>関連Table</x:v>
+      </x:c>
+      <x:c r="I7" s="203" t="str">
+        <x:v>利用元・補足</x:v>
+      </x:c>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="67" t="str">
@@ -4262,10 +3960,12 @@
         <x:v>従業員ページ検索</x:v>
       </x:c>
       <x:c r="C8" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: employeeCode,name,email,departmentId,joinedFrom,joinedTo,status,page,size,sortを型・必須・桁・業務Ruleで検証。3) employees,departments,users,project_membersを参照/更新。4) 参照の境界でCommit/Rollback。5) Page&lt;EmployeeSummary&gt;を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) employees,departments,users,project_membersを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D8" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ関係社員</x:v>
+        <x:v>02／13_API権限対応 API-EMP-001
+Permission: PERM-EMP-READ
+Data Scope: DS-EMP-001</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
         <x:v>参照</x:v>
@@ -4276,8 +3976,17 @@
       <x:c r="G8" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="H8" s="203" t="str">
+        <x:v>employees,departments,users,project_members</x:v>
+      </x:c>
+      <x:c r="I8" s="203" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+    </x:row>
+    <x:row r="9" ht="124" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-EMP-002</x:v>
       </x:c>
@@ -4285,22 +3994,34 @@
         <x:v>従業員詳細</x:v>
       </x:c>
       <x:c r="C9" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id Longを型・必須・桁・業務Ruleで検証。3) employees,departments,projects,tasksを参照/更新。4) 参照の境界でCommit/Rollback。5) EmployeeDetail + projects[] + tasks[]を共通Response形式で返却。</x:v>
+        <x:v>1) 認証・対象社員の参照範囲を確認。2) path idを検証。3) ADMINは全PJ/Task履歴、PMは本人担当未完了PJおよび当該PJ内Taskだけを取得。4) 参照Transaction。5) EmployeeDetailを返却。
+参加履歴の複数行があっても社員詳細のPJ一覧はproject_id単位で重複排除。</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ関係社員</x:v>
+        <x:v>02／13_API権限対応 API-EMP-002
+Permission: PERM-EMP-READ
+Data Scope: DS-EMP-002</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
         <x:v>参照</x:v>
       </x:c>
       <x:c r="F9" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
+        <x:v>COMMON-4040, AUTH-4006</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+      <x:c r="H9" s="241" t="str">
+        <x:v>employees,departments,projects,tasks</x:v>
+      </x:c>
+      <x:c r="I9" s="241" t="str">
+        <x:v>SCR-005, SCR-006</x:v>
+      </x:c>
+      <x:c r="J9" s="241"/>
+      <x:c r="K9" s="241"/>
+      <x:c r="L9" s="241"/>
+    </x:row>
+    <x:row r="10" ht="236" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-EMP-003</x:v>
       </x:c>
@@ -4308,22 +4029,34 @@
         <x:v>従業員登録</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) body: employeeCode,name,nameKana,email,phone,departmentId,position,joinedDate,managerId,username,roleIds,remark; header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) employees,users,user_roles,operation_logsを参照/更新。4) TX-001の境界でCommit/Rollback。5) id,employeeCode,temporaryPasswordを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) employees,users,user_roles,operation_logsを参照/更新。4) TX-001の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。
+Role割当は02／09、秘密値初回/再送は16／28 BR-API-002。</x:v>
       </x:c>
       <x:c r="D10" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-EMP-003
+Permission: PERM-EMP-WRITE
+Data Scope: DS-EMP-003</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
         <x:v>TX-001</x:v>
       </x:c>
       <x:c r="F10" s="67" t="str">
-        <x:v>EMP-4001, EMP-4002, EMP-4003,COMMON-4000, COMMON-4090</x:v>
+        <x:v>EMP-4001, EMP-4002, EMP-4003, EMP-4006,COMMON-4000, COMMON-4090</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+      <x:c r="H10" s="241" t="str">
+        <x:v>employees,users,user_roles,operation_logs</x:v>
+      </x:c>
+      <x:c r="I10" s="241" t="str">
+        <x:v>SCR-004</x:v>
+      </x:c>
+      <x:c r="J10" s="241"/>
+      <x:c r="K10" s="241"/>
+      <x:c r="L10" s="241"/>
+    </x:row>
+    <x:row r="11" ht="156" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-EMP-004</x:v>
       </x:c>
@@ -4331,20 +4064,31 @@
         <x:v>従業員更新</x:v>
       </x:c>
       <x:c r="C11" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: name,nameKana,email,phone,departmentId,position,managerId,remark,versionを型・必須・桁・業務Ruleで検証。3) employees,operation_logsを参照/更新。4) TX-EMP-UPDATEの境界でCommit/Rollback。5) id,versionを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) employees,operation_logsを参照/更新。4) TX-015の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-EMP-004
+Permission: PERM-EMP-WRITE
+Data Scope: DS-EMP-004</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
         <x:v>TX-015</x:v>
       </x:c>
       <x:c r="F11" s="67" t="str">
-        <x:v>EMP-4002,COMMON-4040, COMMON-4090</x:v>
+        <x:v>EMP-4002, EMP-4006,COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H11" s="203" t="str">
+        <x:v>employees,operation_logs</x:v>
+      </x:c>
+      <x:c r="I11" s="203" t="str">
+        <x:v>SCR-005</x:v>
+      </x:c>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="67" t="str">
@@ -4354,22 +4098,33 @@
         <x:v>従業員状態変更</x:v>
       </x:c>
       <x:c r="C12" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: status,leftDate,unfinishedTaskPolicy,reassignmentAssigneeId,versionを型・必須・桁・業務Ruleで検証。3) employees,users,tasks,refresh_tokens / Redisを参照/更新。4) TX-005の境界でCommit/Rollback。5) id,status,versionを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) employees,users,tasks,refresh_tokens / Redisを参照/更新。4) TX-005の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D12" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-EMP-005
+Permission: PERM-EMP-WRITE
+Data Scope: DS-EMP-005</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
         <x:v>TX-005</x:v>
       </x:c>
       <x:c r="F12" s="67" t="str">
-        <x:v>EMP-4004,COMMON-4040, COMMON-4090</x:v>
+        <x:v>EMP-4005, EMP-4006, EMP-4007,COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="H12" s="203" t="str">
+        <x:v>employees,users,tasks,project_members,refresh_tokens,operation_logs / Redis</x:v>
+      </x:c>
+      <x:c r="I12" s="203" t="str">
+        <x:v>SCR-005</x:v>
+      </x:c>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13" ht="166" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-EMP-006</x:v>
       </x:c>
@@ -4377,20 +4132,32 @@
         <x:v>従業員Excel取込</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) multipart: file xlsx &lt;=10MB; header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) employees,users,user_roles,operation_logsを参照/更新。4) TX-EMP-IMPORTの境界でCommit/Rollback。5) total,success,failed,errors[{row,field,code,message}]を共通Response形式で返却。</x:v>
+        <x:v>1) 認証・権限確認。2) File/Header/行数を検証。3) 社員番号・User名は前後空白Trim後の大文字小文字を区別した完全一致、Emailは前後空白Trim後に小文字化し、File内重複Groupの全行を失敗化。4) 各行を独立Transactionで検証・登録し、成功行Commit/失敗行Rollback。上司は取込開始時点の既存在籍社員のみ。5) 件数・成功行・Error明細を返却。
+Role割当は02／09、秘密値初回/再送は16／28 BR-API-002。</x:v>
       </x:c>
       <x:c r="D13" s="67" t="str">
-        <x:v>管理者のみ; 行単位検証・行単位Transaction。成功行のみCommitし、失敗行はRollbackしてError明細返却</x:v>
+        <x:v>02／13_API権限対応 API-EMP-006
+Permission: PERM-EMP-WRITE
+Data Scope: DS-EMP-006</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
         <x:v>TX-016</x:v>
       </x:c>
       <x:c r="F13" s="67" t="str">
-        <x:v>FILE-4001, FILE-4002,EMP-4001, EMP-4002, EMP-4003</x:v>
+        <x:v>FILE-4001, FILE-4002, EMP-4001, EMP-4002, EMP-4003, EMP-4006, COMMON-4000</x:v>
       </x:c>
       <x:c r="G13" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H13" s="241" t="str">
+        <x:v>employees,users,user_roles,operation_logs</x:v>
+      </x:c>
+      <x:c r="I13" s="241" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="J13" s="241"/>
+      <x:c r="K13" s="241"/>
+      <x:c r="L13" s="241"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="67" t="str">
@@ -4400,10 +4167,12 @@
         <x:v>従業員Excel出力</x:v>
       </x:c>
       <x:c r="C14" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: API-EMP-001と同一検索条件を型・必須・桁・業務Ruleで検証。3) employees,departments,users,rolesを参照/更新。4) 参照の境界でCommit/Rollback。5) xlsx fileを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) employees,departments,users,rolesを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D14" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-EMP-007
+Permission: PERM-EMP-READ
+Data Scope: DS-EMP-007</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
         <x:v>参照</x:v>
@@ -4414,6 +4183,15 @@
       <x:c r="G14" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H14" s="203" t="str">
+        <x:v>employees,departments,users,roles</x:v>
+      </x:c>
+      <x:c r="I14" s="203" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="67" t="str">
@@ -4423,10 +4201,12 @@
         <x:v>部門Tree取得</x:v>
       </x:c>
       <x:c r="C15" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: includeDisabled Boolean=falseを型・必須・桁・業務Ruleで検証。3) departments / Redisを参照/更新。4) 参照の境界でCommit/Rollback。5) DepartmentNode[]を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) departments / Redisを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D15" s="67" t="str">
-        <x:v>一般=有効部門, 管理者=指定可</x:v>
+        <x:v>02／13_API権限対応 API-DEPT-001
+Permission: -（認証済共通）
+Data Scope: DS-DEPT-001</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
         <x:v>参照</x:v>
@@ -4437,6 +4217,15 @@
       <x:c r="G15" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H15" s="203" t="str">
+        <x:v>departments / Redis</x:v>
+      </x:c>
+      <x:c r="I15" s="203" t="str">
+        <x:v>SCR-007</x:v>
+      </x:c>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="67" t="str">
@@ -4446,10 +4235,12 @@
         <x:v>部門詳細</x:v>
       </x:c>
       <x:c r="C16" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id Longを型・必須・桁・業務Ruleで検証。3) departments,employeesを参照/更新。4) 参照の境界でCommit/Rollback。5) id,code,name,parentId,managerId,displayOrder,status,versionを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) departments,employeesを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D16" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-DEPT-002
+Permission: PERM-DEPT-WRITE
+Data Scope: DS-DEPT-002</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
         <x:v>参照</x:v>
@@ -4460,8 +4251,17 @@
       <x:c r="G16" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="H16" s="203" t="str">
+        <x:v>departments,employees</x:v>
+      </x:c>
+      <x:c r="I16" s="203" t="str">
+        <x:v>SCR-007</x:v>
+      </x:c>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="52" customHeight="1">
       <x:c r="A17" s="67" t="str">
         <x:v>API-DEPT-003</x:v>
       </x:c>
@@ -4469,22 +4269,33 @@
         <x:v>部門登録</x:v>
       </x:c>
       <x:c r="C17" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) body: departmentCode,name,parentId,managerId,displayOrder,status; header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) departments,operation_logs / Redisを参照/更新。4) TX-DEPTの境界でCommit/Rollback。5) id,versionを共通Response形式で返却。</x:v>
+        <x:v>1) 認証・権限確認。2) status=ACTIVE固定、親部門/責任者/一意性を検証。3) 部門登録。4) TX-017。5) id/versionを返却。</x:v>
       </x:c>
       <x:c r="D17" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-DEPT-003
+Permission: PERM-DEPT-WRITE
+Data Scope: DS-DEPT-003</x:v>
       </x:c>
       <x:c r="E17" s="67" t="str">
         <x:v>TX-017</x:v>
       </x:c>
       <x:c r="F17" s="67" t="str">
-        <x:v>DEPT-4001, DEPT-4002,COMMON-4000, COMMON-4090</x:v>
+        <x:v>DEPT-4001, COMMON-4000, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="G17" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="30" customHeight="1">
+      <x:c r="H17" s="203" t="str">
+        <x:v>departments,operation_logs / Redis</x:v>
+      </x:c>
+      <x:c r="I17" s="203" t="str">
+        <x:v>SCR-007</x:v>
+      </x:c>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
+    </x:row>
+    <x:row r="18" ht="78" customHeight="1">
       <x:c r="A18" s="67" t="str">
         <x:v>API-DEPT-004</x:v>
       </x:c>
@@ -4492,22 +4303,33 @@
         <x:v>部門更新</x:v>
       </x:c>
       <x:c r="C18" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: name,parentId,managerId,displayOrder,status,versionを型・必須・桁・業務Ruleで検証。3) departments,operation_logs / Redisを参照/更新。4) TX-DEPTの境界でCommit/Rollback。5) id,versionを共通Response形式で返却。</x:v>
+        <x:v>1) 認証・権限確認。2) 通常更新はstatus据置、停止時はACTIVE→DISABLEDのみを検証。3) 名称等を更新。4) TX-017。5) id/versionを返却。DISABLED→ACTIVEは禁止。</x:v>
       </x:c>
       <x:c r="D18" s="67" t="str">
-        <x:v>自己・子孫を親に設定不可</x:v>
+        <x:v>02／13_API権限対応 API-DEPT-004
+Permission: PERM-DEPT-WRITE
+Data Scope: DS-DEPT-004</x:v>
       </x:c>
       <x:c r="E18" s="67" t="str">
         <x:v>TX-017</x:v>
       </x:c>
       <x:c r="F18" s="67" t="str">
-        <x:v>DEPT-4001, DEPT-4002,COMMON-4040, COMMON-4090</x:v>
+        <x:v>DEPT-4001, DEPT-4002, DEPT-4003, DEPT-4004,COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="G18" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" ht="30" customHeight="1">
+      <x:c r="H18" s="203" t="str">
+        <x:v>departments,employees,operation_logs / Redis</x:v>
+      </x:c>
+      <x:c r="I18" s="203" t="str">
+        <x:v>SCR-007</x:v>
+      </x:c>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
+    </x:row>
+    <x:row r="19" ht="52" customHeight="1">
       <x:c r="A19" s="67" t="str">
         <x:v>API-DEPT-005</x:v>
       </x:c>
@@ -4515,20 +4337,31 @@
         <x:v>部門削除</x:v>
       </x:c>
       <x:c r="C19" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; query: versionを型・必須・桁・業務Ruleで検証。3) departments,employees,projects / Redisを参照/更新。4) TX-DEPTの境界でCommit/Rollback。5) 204 No Contentを共通Response形式で返却。</x:v>
+        <x:v>1) 認証・権限確認。2) Root以外、社員履歴0件、子部門0件、version一致を検証。3) 部門を論理削除。4) TX-017。5) 204を返却。</x:v>
       </x:c>
       <x:c r="D19" s="67" t="str">
-        <x:v>社員・子部門・PJ関連なし</x:v>
+        <x:v>02／13_API権限対応 API-DEPT-005
+Permission: PERM-DEPT-WRITE
+Data Scope: DS-DEPT-005</x:v>
       </x:c>
       <x:c r="E19" s="67" t="str">
         <x:v>TX-017</x:v>
       </x:c>
       <x:c r="F19" s="67" t="str">
-        <x:v>DEPT-4002, DEPT-4003,COMMON-4090</x:v>
+        <x:v>DEPT-4002, DEPT-4003, DEPT-4004,COMMON-4090</x:v>
       </x:c>
       <x:c r="G19" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H19" s="203" t="str">
+        <x:v>departments,employees,operation_logs / Redis</x:v>
+      </x:c>
+      <x:c r="I19" s="203" t="str">
+        <x:v>SCR-007</x:v>
+      </x:c>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4539,7 +4372,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4566,6 +4399,9 @@
       <x:c r="G1" s="68"/>
       <x:c r="H1" s="68"/>
       <x:c r="I1" s="68"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="68"/>
@@ -4577,6 +4413,9 @@
       <x:c r="G2" s="68"/>
       <x:c r="H2" s="68"/>
       <x:c r="I2" s="68"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="62" t="str">
@@ -4587,8 +4426,8 @@
       </x:c>
       <x:c r="C3" s="63"/>
       <x:c r="D3" s="63"/>
-      <x:c r="E3" s="62" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="E3" s="248" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="F3" s="63" t="str">
         <x:v>CW-BD-FILE-EMP</x:v>
@@ -4596,13 +4435,16 @@
       <x:c r="G3" s="63"/>
       <x:c r="H3" s="63"/>
       <x:c r="I3" s="63"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="62" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="63"/>
@@ -4610,11 +4452,14 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="F4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="G4" s="63"/>
       <x:c r="H4" s="63"/>
       <x:c r="I4" s="63"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="64"/>
@@ -4626,6 +4471,9 @@
       <x:c r="G5" s="64"/>
       <x:c r="H5" s="64"/>
       <x:c r="I5" s="64"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="65" t="str">
@@ -4639,6 +4487,9 @@
       <x:c r="G6" s="65"/>
       <x:c r="H6" s="65"/>
       <x:c r="I6" s="65"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="66" t="str">
@@ -4666,8 +4517,11 @@
         <x:v>Import処理</x:v>
       </x:c>
       <x:c r="I7" s="66" t="str">
-        <x:v>Export</x:v>
-      </x:c>
+        <x:v>Exportとの関係</x:v>
+      </x:c>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="67" t="n">
@@ -4692,11 +4546,14 @@
         <x:v>一意/空白不可</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
-        <x:v>新規のみ。既存番号はError</x:v>
+        <x:v>前後空白Trim後、大文字小文字を区別して一意/空白不可</x:v>
       </x:c>
       <x:c r="I8" s="67" t="str">
-        <x:v>○</x:v>
-      </x:c>
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
+      </x:c>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="67" t="n">
@@ -4724,8 +4581,11 @@
         <x:v>Trim後登録</x:v>
       </x:c>
       <x:c r="I9" s="67" t="str">
-        <x:v>○</x:v>
-      </x:c>
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
+      </x:c>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="67" t="n">
@@ -4753,8 +4613,11 @@
         <x:v>Trim後登録</x:v>
       </x:c>
       <x:c r="I10" s="67" t="str">
-        <x:v>○</x:v>
-      </x:c>
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
+      </x:c>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="67" t="n">
@@ -4779,11 +4642,14 @@
         <x:v>形式/一意</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
-        <x:v>小文字化して比較</x:v>
+        <x:v>形式/前後空白Trim後に小文字化して一意</x:v>
       </x:c>
       <x:c r="I11" s="67" t="str">
-        <x:v>○</x:v>
-      </x:c>
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
+      </x:c>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="67" t="n">
@@ -4811,8 +4677,11 @@
         <x:v>文字列保持</x:v>
       </x:c>
       <x:c r="I12" s="67" t="str">
-        <x:v>○</x:v>
-      </x:c>
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
+      </x:c>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="67" t="n">
@@ -4840,8 +4709,11 @@
         <x:v>department_idへ変換</x:v>
       </x:c>
       <x:c r="I13" s="67" t="str">
-        <x:v>○</x:v>
-      </x:c>
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
+      </x:c>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="67" t="n">
@@ -4869,8 +4741,11 @@
         <x:v>Trim後登録</x:v>
       </x:c>
       <x:c r="I14" s="67" t="str">
-        <x:v>○</x:v>
-      </x:c>
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
+      </x:c>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="67" t="n">
@@ -4892,14 +4767,17 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G15" s="67" t="str">
-        <x:v>実在日</x:v>
+        <x:v>実在日/System日付以下</x:v>
       </x:c>
       <x:c r="H15" s="67" t="str">
-        <x:v>DATE変換</x:v>
+        <x:v>DATE変換。未来日はError</x:v>
       </x:c>
       <x:c r="I15" s="67" t="str">
-        <x:v>○</x:v>
-      </x:c>
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
+      </x:c>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="67" t="n">
@@ -4921,14 +4799,17 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G16" s="67" t="str">
-        <x:v>在籍社員存在</x:v>
+        <x:v>取込開始時点の既存在籍社員。File内新規参照不可</x:v>
       </x:c>
       <x:c r="H16" s="67" t="str">
-        <x:v>manager_idへ変換</x:v>
+        <x:v>manager_idへ変換。不正時は行Error</x:v>
       </x:c>
       <x:c r="I16" s="67" t="str">
-        <x:v>○</x:v>
-      </x:c>
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
+      </x:c>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="67" t="n">
@@ -4953,13 +4834,13 @@
         <x:v>一意</x:v>
       </x:c>
       <x:c r="H17" s="67" t="str">
-        <x:v>User作成</x:v>
+        <x:v>前後空白Trim後、大文字小文字を区別して一意</x:v>
       </x:c>
       <x:c r="I17" s="67" t="str">
-        <x:v>○</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="30" customHeight="1">
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="40" customHeight="1">
       <x:c r="A18" s="67" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -4979,14 +4860,17 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="G18" s="67" t="str">
-        <x:v>カンマ区切り/有効Role</x:v>
+        <x:v>有効Code、内蔵Roleを1つ以上。Comma区切り、重複不可。</x:v>
       </x:c>
       <x:c r="H18" s="67" t="str">
         <x:v>user_roles作成</x:v>
       </x:c>
       <x:c r="I18" s="67" t="str">
-        <x:v>○</x:v>
-      </x:c>
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
+      </x:c>
+      <x:c r="J18" s="241"/>
+      <x:c r="K18" s="241"/>
+      <x:c r="L18" s="241"/>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
       <x:c r="A19" s="67" t="n">
@@ -5014,7 +4898,7 @@
         <x:v>Trim後登録</x:v>
       </x:c>
       <x:c r="I19" s="67" t="str">
-        <x:v>○</x:v>
+        <x:v>出力列は下記のExport専用仕様を参照</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -5028,9 +4912,10 @@
       <x:c r="H20" s="64"/>
       <x:c r="I20" s="64"/>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="88" t="str">
-        <x:v>Sheet名=employees、Header=1行目、Data=2行目以降、最大1,000件。全行検証後に一括Commitし、1件でもErrorなら全件Rollback。ErrorはAPI Responseのrow/field/code/messageで返却する。</x:v>
+    <x:row r="21" ht="100" customHeight="1">
+      <x:c r="A21" s="243" t="str">
+        <x:v>Import：xlsx、10MB以下。先頭Sheet名はemployees、1行目はC列Field名を列No.順に記載、2行目以降がData。完全空行を除き1～1000行。Sheet名・Header・形式不正は登録開始前にFile全体を拒否する。全行のFile内重複を先に検証し、重複Group全行を失敗とする。正常候補行は行単位Transactionで成功行Commit／失敗行Rollback。System障害時は処理中行Rollback、未処理行を失敗として終了し、既Commit行は保持。行番号・項目・Error Code・Messageを結果へ返す。
+Export：Sheet名employees、Headerは下表の日本語列名順。検索条件と権限範囲の全件（Page指定無視）を社員番号昇順で出力。0件はMSG-I-011、50000件超は条件絞込案内。Password/Tokenは出力しない。</x:v>
       </x:c>
       <x:c r="B21" s="89"/>
       <x:c r="C21" s="89"/>
@@ -5041,7 +4926,7 @@
       <x:c r="H21" s="89"/>
       <x:c r="I21" s="90"/>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" ht="20" customHeight="1">
       <x:c r="A22" s="91"/>
       <x:c r="B22" s="92"/>
       <x:c r="C22" s="92"/>
@@ -5051,6 +4936,412 @@
       <x:c r="G22" s="92"/>
       <x:c r="H22" s="92"/>
       <x:c r="I22" s="93"/>
+    </x:row>
+    <x:row r="23" ht="110" customHeight="1">
+      <x:c r="A23" s="241" t="str">
+        <x:v>Export専用仕様</x:v>
+      </x:c>
+      <x:c r="B23" s="241" t="str">
+        <x:v>列順</x:v>
+      </x:c>
+      <x:c r="C23" s="241" t="str">
+        <x:v>Header</x:v>
+      </x:c>
+      <x:c r="D23" s="241" t="str">
+        <x:v>値/形式</x:v>
+      </x:c>
+      <x:c r="E23" s="241" t="str">
+        <x:v>対象</x:v>
+      </x:c>
+      <x:c r="F23" s="241" t="str">
+        <x:v>並び順</x:v>
+      </x:c>
+      <x:c r="G23" s="241" t="str">
+        <x:v>上限</x:v>
+      </x:c>
+      <x:c r="H23" s="241" t="str">
+        <x:v>0件</x:v>
+      </x:c>
+      <x:c r="I23" s="241" t="str">
+        <x:v>備考</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="110" customHeight="1">
+      <x:c r="A24" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B24" s="241" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C24" s="241" t="str">
+        <x:v>社員番号</x:v>
+      </x:c>
+      <x:c r="D24" s="241" t="str">
+        <x:v>画面検索結果の対応値</x:v>
+      </x:c>
+      <x:c r="E24" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F24" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G24" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H24" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I24" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="110" customHeight="1">
+      <x:c r="A25" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B25" s="241" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C25" s="241" t="str">
+        <x:v>氏名</x:v>
+      </x:c>
+      <x:c r="D25" s="241" t="str">
+        <x:v>画面検索結果の対応値</x:v>
+      </x:c>
+      <x:c r="E25" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F25" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G25" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H25" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I25" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="110" customHeight="1">
+      <x:c r="A26" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B26" s="241" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C26" s="241" t="str">
+        <x:v>氏名カナ</x:v>
+      </x:c>
+      <x:c r="D26" s="241" t="str">
+        <x:v>画面検索結果の対応値</x:v>
+      </x:c>
+      <x:c r="E26" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F26" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G26" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H26" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I26" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="110" customHeight="1">
+      <x:c r="A27" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B27" s="241" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="241" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="D27" s="241" t="str">
+        <x:v>画面検索結果の対応値</x:v>
+      </x:c>
+      <x:c r="E27" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F27" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G27" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H27" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I27" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="110" customHeight="1">
+      <x:c r="A28" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B28" s="241" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C28" s="241" t="str">
+        <x:v>電話</x:v>
+      </x:c>
+      <x:c r="D28" s="241" t="str">
+        <x:v>画面検索結果の対応値</x:v>
+      </x:c>
+      <x:c r="E28" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F28" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G28" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H28" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I28" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="110" customHeight="1">
+      <x:c r="A29" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B29" s="241" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C29" s="241" t="str">
+        <x:v>部門番号</x:v>
+      </x:c>
+      <x:c r="D29" s="241" t="str">
+        <x:v>画面検索結果の対応値</x:v>
+      </x:c>
+      <x:c r="E29" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F29" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G29" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H29" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I29" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="110" customHeight="1">
+      <x:c r="A30" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B30" s="241" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C30" s="241" t="str">
+        <x:v>部門名</x:v>
+      </x:c>
+      <x:c r="D30" s="241" t="str">
+        <x:v>画面検索結果の対応値</x:v>
+      </x:c>
+      <x:c r="E30" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F30" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G30" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H30" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I30" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="110" customHeight="1">
+      <x:c r="A31" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B31" s="241" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C31" s="241" t="str">
+        <x:v>役職</x:v>
+      </x:c>
+      <x:c r="D31" s="241" t="str">
+        <x:v>画面検索結果の対応値</x:v>
+      </x:c>
+      <x:c r="E31" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F31" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G31" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H31" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I31" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="110" customHeight="1">
+      <x:c r="A32" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B32" s="241" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C32" s="241" t="str">
+        <x:v>入社日</x:v>
+      </x:c>
+      <x:c r="D32" s="241" t="str">
+        <x:v>yyyy-MM-dd（未設定は空欄）</x:v>
+      </x:c>
+      <x:c r="E32" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F32" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G32" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H32" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I32" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="110" customHeight="1">
+      <x:c r="A33" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B33" s="241" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C33" s="241" t="str">
+        <x:v>退職日</x:v>
+      </x:c>
+      <x:c r="D33" s="241" t="str">
+        <x:v>yyyy-MM-dd（未設定は空欄）</x:v>
+      </x:c>
+      <x:c r="E33" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F33" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G33" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H33" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I33" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="110" customHeight="1">
+      <x:c r="A34" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B34" s="241" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C34" s="241" t="str">
+        <x:v>在籍状態</x:v>
+      </x:c>
+      <x:c r="D34" s="241" t="str">
+        <x:v>画面検索結果の対応値</x:v>
+      </x:c>
+      <x:c r="E34" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F34" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G34" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H34" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I34" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="110" customHeight="1">
+      <x:c r="A35" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B35" s="241" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C35" s="241" t="str">
+        <x:v>上司社員番号</x:v>
+      </x:c>
+      <x:c r="D35" s="241" t="str">
+        <x:v>画面検索結果の対応値</x:v>
+      </x:c>
+      <x:c r="E35" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F35" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G35" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H35" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I35" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="110" customHeight="1">
+      <x:c r="A36" s="241" t="str">
+        <x:v>Export</x:v>
+      </x:c>
+      <x:c r="B36" s="241" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C36" s="241" t="str">
+        <x:v>備考</x:v>
+      </x:c>
+      <x:c r="D36" s="241" t="str">
+        <x:v>画面検索結果の対応値</x:v>
+      </x:c>
+      <x:c r="E36" s="241" t="str">
+        <x:v>検索範囲全件</x:v>
+      </x:c>
+      <x:c r="F36" s="241" t="str">
+        <x:v>社員番号昇順</x:v>
+      </x:c>
+      <x:c r="G36" s="241" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H36" s="241" t="str">
+        <x:v>未生成／MSG-I-011</x:v>
+      </x:c>
+      <x:c r="I36" s="241" t="str">
+        <x:v>取込と別形式</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5062,7 +5353,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5093,6 +5384,7 @@
       <x:c r="I1" s="172"/>
       <x:c r="J1" s="172"/>
       <x:c r="K1" s="172"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="172"/>
@@ -5106,6 +5398,7 @@
       <x:c r="I2" s="172"/>
       <x:c r="J2" s="172"/>
       <x:c r="K2" s="172"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="174" t="str">
@@ -5117,8 +5410,8 @@
       <x:c r="C3" s="139"/>
       <x:c r="D3" s="139"/>
       <x:c r="E3" s="139"/>
-      <x:c r="F3" s="174" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="F3" s="248" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="G3" s="139" t="str">
         <x:v>CW-BD-11-FIELD</x:v>
@@ -5127,13 +5420,14 @@
       <x:c r="I3" s="139"/>
       <x:c r="J3" s="139"/>
       <x:c r="K3" s="139"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="174" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="63" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="139"/>
@@ -5141,13 +5435,28 @@
       <x:c r="F4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="G4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="G4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="H4" s="139"/>
       <x:c r="I4" s="139"/>
       <x:c r="J4" s="139"/>
       <x:c r="K4" s="139"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5"/>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="175" t="str">
@@ -5163,6 +5472,7 @@
       <x:c r="I6" s="175"/>
       <x:c r="J6" s="175"/>
       <x:c r="K6" s="175"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="181" t="str">
@@ -5198,6 +5508,7 @@
       <x:c r="K7" s="181" t="str">
         <x:v>DB／生成元</x:v>
       </x:c>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="67" t="str">
@@ -5233,6 +5544,7 @@
       <x:c r="K8" s="67" t="str">
         <x:v>employees.employee_code</x:v>
       </x:c>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="67" t="str">
@@ -5268,6 +5580,7 @@
       <x:c r="K9" s="67" t="str">
         <x:v>employees.name</x:v>
       </x:c>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="67" t="str">
@@ -5303,6 +5616,7 @@
       <x:c r="K10" s="67" t="str">
         <x:v>employees.email</x:v>
       </x:c>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="67" t="str">
@@ -5338,6 +5652,7 @@
       <x:c r="K11" s="67" t="str">
         <x:v>employees.department_id</x:v>
       </x:c>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="67" t="str">
@@ -5373,6 +5688,7 @@
       <x:c r="K12" s="67" t="str">
         <x:v>検索条件（employees.joined_date From）</x:v>
       </x:c>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="67" t="str">
@@ -5408,6 +5724,7 @@
       <x:c r="K13" s="67" t="str">
         <x:v>検索条件（employees.joined_date To）</x:v>
       </x:c>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="67" t="str">
@@ -5443,6 +5760,7 @@
       <x:c r="K14" s="67" t="str">
         <x:v>employees.employment_status</x:v>
       </x:c>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="67" t="str">
@@ -5478,6 +5796,7 @@
       <x:c r="K15" s="67" t="str">
         <x:v>検索条件</x:v>
       </x:c>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="67" t="str">
@@ -5513,6 +5832,7 @@
       <x:c r="K16" s="67" t="str">
         <x:v>検索条件</x:v>
       </x:c>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="67" t="str">
@@ -5548,6 +5868,7 @@
       <x:c r="K17" s="67" t="str">
         <x:v>検索条件</x:v>
       </x:c>
+      <x:c r="L17"/>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="67" t="str">
@@ -5583,6 +5904,7 @@
       <x:c r="K18" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L18"/>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="67" t="str">
@@ -5618,6 +5940,7 @@
       <x:c r="K19" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L19"/>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="67" t="str">
@@ -5653,6 +5976,7 @@
       <x:c r="K20" s="67" t="str">
         <x:v>Response DTO</x:v>
       </x:c>
+      <x:c r="L20"/>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="67" t="str">
@@ -5688,6 +6012,7 @@
       <x:c r="K21" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L21"/>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="67" t="str">
@@ -5723,6 +6048,7 @@
       <x:c r="K22" s="67" t="str">
         <x:v>Log traceId</x:v>
       </x:c>
+      <x:c r="L22"/>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="67" t="str">
@@ -5758,6 +6084,7 @@
       <x:c r="K23" s="67" t="str">
         <x:v>-</x:v>
       </x:c>
+      <x:c r="L23"/>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="67" t="str">
@@ -5793,6 +6120,7 @@
       <x:c r="K24" s="67" t="str">
         <x:v>employees.id</x:v>
       </x:c>
+      <x:c r="L24"/>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="67" t="str">
@@ -5828,6 +6156,7 @@
       <x:c r="K25" s="67" t="str">
         <x:v>employees.employee_code</x:v>
       </x:c>
+      <x:c r="L25"/>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="67" t="str">
@@ -5863,6 +6192,7 @@
       <x:c r="K26" s="67" t="str">
         <x:v>employees.name</x:v>
       </x:c>
+      <x:c r="L26"/>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="67" t="str">
@@ -5898,6 +6228,7 @@
       <x:c r="K27" s="67" t="str">
         <x:v>employees.name_kana</x:v>
       </x:c>
+      <x:c r="L27"/>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="67" t="str">
@@ -5933,6 +6264,7 @@
       <x:c r="K28" s="67" t="str">
         <x:v>employees.email</x:v>
       </x:c>
+      <x:c r="L28"/>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="67" t="str">
@@ -5968,6 +6300,7 @@
       <x:c r="K29" s="67" t="str">
         <x:v>employees.department_id</x:v>
       </x:c>
+      <x:c r="L29"/>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="67" t="str">
@@ -6003,6 +6336,7 @@
       <x:c r="K30" s="67" t="str">
         <x:v>departments.department_name</x:v>
       </x:c>
+      <x:c r="L30"/>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="67" t="str">
@@ -6038,6 +6372,7 @@
       <x:c r="K31" s="67" t="str">
         <x:v>employees.position</x:v>
       </x:c>
+      <x:c r="L31"/>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="67" t="str">
@@ -6073,6 +6408,7 @@
       <x:c r="K32" s="67" t="str">
         <x:v>employees.employment_status</x:v>
       </x:c>
+      <x:c r="L32"/>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="67" t="str">
@@ -6108,6 +6444,7 @@
       <x:c r="K33" s="67" t="str">
         <x:v>employees.joined_date</x:v>
       </x:c>
+      <x:c r="L33"/>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="67" t="str">
@@ -6143,6 +6480,7 @@
       <x:c r="K34" s="67" t="str">
         <x:v>employees.left_date</x:v>
       </x:c>
+      <x:c r="L34"/>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="67" t="str">
@@ -6178,6 +6516,7 @@
       <x:c r="K35" s="67" t="str">
         <x:v>employees.version</x:v>
       </x:c>
+      <x:c r="L35"/>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="67" t="str">
@@ -6213,6 +6552,7 @@
       <x:c r="K36" s="67" t="str">
         <x:v>共通Page</x:v>
       </x:c>
+      <x:c r="L36"/>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" s="67" t="str">
@@ -6248,6 +6588,7 @@
       <x:c r="K37" s="67" t="str">
         <x:v>共通Page</x:v>
       </x:c>
+      <x:c r="L37"/>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="67" t="str">
@@ -6283,6 +6624,7 @@
       <x:c r="K38" s="67" t="str">
         <x:v>共通Page</x:v>
       </x:c>
+      <x:c r="L38"/>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
       <x:c r="A39" s="67" t="str">
@@ -6318,6 +6660,7 @@
       <x:c r="K39" s="67" t="str">
         <x:v>共通Page</x:v>
       </x:c>
+      <x:c r="L39"/>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="67" t="str">
@@ -6353,6 +6696,7 @@
       <x:c r="K40" s="67" t="str">
         <x:v>共通Page</x:v>
       </x:c>
+      <x:c r="L40"/>
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="67" t="str">
@@ -6388,6 +6732,7 @@
       <x:c r="K41" s="67" t="str">
         <x:v>共通Page</x:v>
       </x:c>
+      <x:c r="L41"/>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
       <x:c r="A42" s="67" t="str">
@@ -6423,6 +6768,7 @@
       <x:c r="K42" s="67" t="str">
         <x:v>employees.id</x:v>
       </x:c>
+      <x:c r="L42"/>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
       <x:c r="A43" s="67" t="str">
@@ -6458,6 +6804,7 @@
       <x:c r="K43" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L43"/>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
       <x:c r="A44" s="67" t="str">
@@ -6493,6 +6840,7 @@
       <x:c r="K44" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L44"/>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
       <x:c r="A45" s="67" t="str">
@@ -6528,6 +6876,7 @@
       <x:c r="K45" s="67" t="str">
         <x:v>Response DTO</x:v>
       </x:c>
+      <x:c r="L45"/>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
       <x:c r="A46" s="67" t="str">
@@ -6563,6 +6912,7 @@
       <x:c r="K46" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L46"/>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="67" t="str">
@@ -6598,6 +6948,7 @@
       <x:c r="K47" s="67" t="str">
         <x:v>Log traceId</x:v>
       </x:c>
+      <x:c r="L47"/>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
       <x:c r="A48" s="67" t="str">
@@ -6633,6 +6984,7 @@
       <x:c r="K48" s="67" t="str">
         <x:v>employees.id</x:v>
       </x:c>
+      <x:c r="L48"/>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
       <x:c r="A49" s="67" t="str">
@@ -6668,6 +7020,7 @@
       <x:c r="K49" s="67" t="str">
         <x:v>employees.employee_code</x:v>
       </x:c>
+      <x:c r="L49"/>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
       <x:c r="A50" s="67" t="str">
@@ -6703,6 +7056,7 @@
       <x:c r="K50" s="67" t="str">
         <x:v>employees.name</x:v>
       </x:c>
+      <x:c r="L50"/>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="67" t="str">
@@ -6738,6 +7092,7 @@
       <x:c r="K51" s="67" t="str">
         <x:v>employees.name_kana</x:v>
       </x:c>
+      <x:c r="L51"/>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
       <x:c r="A52" s="67" t="str">
@@ -6773,6 +7128,7 @@
       <x:c r="K52" s="67" t="str">
         <x:v>employees.email</x:v>
       </x:c>
+      <x:c r="L52"/>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
       <x:c r="A53" s="67" t="str">
@@ -6808,6 +7164,7 @@
       <x:c r="K53" s="67" t="str">
         <x:v>employees.department_id</x:v>
       </x:c>
+      <x:c r="L53"/>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
       <x:c r="A54" s="67" t="str">
@@ -6843,6 +7200,7 @@
       <x:c r="K54" s="67" t="str">
         <x:v>departments.department_name</x:v>
       </x:c>
+      <x:c r="L54"/>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
       <x:c r="A55" s="67" t="str">
@@ -6878,6 +7236,7 @@
       <x:c r="K55" s="67" t="str">
         <x:v>employees.position</x:v>
       </x:c>
+      <x:c r="L55"/>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
       <x:c r="A56" s="67" t="str">
@@ -6913,6 +7272,7 @@
       <x:c r="K56" s="67" t="str">
         <x:v>employees.employment_status</x:v>
       </x:c>
+      <x:c r="L56"/>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
       <x:c r="A57" s="67" t="str">
@@ -6948,6 +7308,7 @@
       <x:c r="K57" s="67" t="str">
         <x:v>employees.joined_date</x:v>
       </x:c>
+      <x:c r="L57"/>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
       <x:c r="A58" s="67" t="str">
@@ -6983,6 +7344,7 @@
       <x:c r="K58" s="67" t="str">
         <x:v>employees.left_date</x:v>
       </x:c>
+      <x:c r="L58"/>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
       <x:c r="A59" s="67" t="str">
@@ -7018,6 +7380,7 @@
       <x:c r="K59" s="67" t="str">
         <x:v>employees.version</x:v>
       </x:c>
+      <x:c r="L59"/>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
       <x:c r="A60" s="67" t="str">
@@ -7053,6 +7416,7 @@
       <x:c r="K60" s="67" t="str">
         <x:v>employees.phone_number</x:v>
       </x:c>
+      <x:c r="L60"/>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
       <x:c r="A61" s="67" t="str">
@@ -7088,6 +7452,7 @@
       <x:c r="K61" s="67" t="str">
         <x:v>employees.manager_id</x:v>
       </x:c>
+      <x:c r="L61"/>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
       <x:c r="A62" s="67" t="str">
@@ -7123,8 +7488,9 @@
       <x:c r="K62" s="67" t="str">
         <x:v>employees.remark</x:v>
       </x:c>
-    </x:row>
-    <x:row r="63" ht="15" hidden="0" customHeight="1">
+      <x:c r="L62"/>
+    </x:row>
+    <x:row r="63" ht="39" hidden="0" customHeight="1">
       <x:c r="A63" s="67" t="str">
         <x:v>API-EMP-002</x:v>
       </x:c>
@@ -7153,11 +7519,12 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J63" s="67" t="str">
-        <x:v>参加PJ</x:v>
+        <x:v>権限範囲の参加履歴を全件返す。画面で20件ずつ表示。状態Code降順、開始日降順、id昇順。0件は[]。</x:v>
       </x:c>
       <x:c r="K63" s="67" t="str">
         <x:v>project_members/projects</x:v>
       </x:c>
+      <x:c r="L63"/>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
       <x:c r="A64" s="67" t="str">
@@ -7193,6 +7560,7 @@
       <x:c r="K64" s="67" t="str">
         <x:v>projects.id</x:v>
       </x:c>
+      <x:c r="L64"/>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="67" t="str">
@@ -7228,6 +7596,7 @@
       <x:c r="K65" s="67" t="str">
         <x:v>projects.project_code</x:v>
       </x:c>
+      <x:c r="L65"/>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="67" t="str">
@@ -7249,7 +7618,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G66" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H66" s="67" t="str">
         <x:v>-</x:v>
@@ -7263,6 +7632,7 @@
       <x:c r="K66" s="67" t="str">
         <x:v>projects.project_name</x:v>
       </x:c>
+      <x:c r="L66"/>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="67" t="str">
@@ -7298,6 +7668,7 @@
       <x:c r="K67" s="67" t="str">
         <x:v>projects.manager_id</x:v>
       </x:c>
+      <x:c r="L67"/>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="67" t="str">
@@ -7333,8 +7704,9 @@
       <x:c r="K68" s="67" t="str">
         <x:v>employees.name</x:v>
       </x:c>
-    </x:row>
-    <x:row r="69" ht="15" hidden="0" customHeight="1">
+      <x:c r="L68"/>
+    </x:row>
+    <x:row r="69" ht="52" hidden="0" customHeight="1">
       <x:c r="A69" s="67" t="str">
         <x:v>API-EMP-002</x:v>
       </x:c>
@@ -7363,11 +7735,12 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J69" s="67" t="str">
-        <x:v>担当Task</x:v>
+        <x:v>権限範囲の担当Task（未削除、完了/取消含む）を全件返す。画面で20件ずつ表示。updatedAt降順、id昇順。0件は[]。</x:v>
       </x:c>
       <x:c r="K69" s="67" t="str">
         <x:v>tasks</x:v>
       </x:c>
+      <x:c r="L69"/>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
       <x:c r="A70" s="67" t="str">
@@ -7403,6 +7776,7 @@
       <x:c r="K70" s="67" t="str">
         <x:v>tasks.id</x:v>
       </x:c>
+      <x:c r="L70"/>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="67" t="str">
@@ -7438,6 +7812,7 @@
       <x:c r="K71" s="67" t="str">
         <x:v>tasks.task_code</x:v>
       </x:c>
+      <x:c r="L71"/>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="67" t="str">
@@ -7473,6 +7848,7 @@
       <x:c r="K72" s="67" t="str">
         <x:v>tasks.project_id</x:v>
       </x:c>
+      <x:c r="L72"/>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="67" t="str">
@@ -7494,7 +7870,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G73" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H73" s="67" t="str">
         <x:v>-</x:v>
@@ -7508,6 +7884,7 @@
       <x:c r="K73" s="67" t="str">
         <x:v>projects.project_name</x:v>
       </x:c>
+      <x:c r="L73"/>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
       <x:c r="A74" s="67" t="str">
@@ -7543,6 +7920,7 @@
       <x:c r="K74" s="67" t="str">
         <x:v>tasks.title</x:v>
       </x:c>
+      <x:c r="L74"/>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="67" t="str">
@@ -7578,6 +7956,7 @@
       <x:c r="K75" s="67" t="str">
         <x:v>tasks.assignee_id</x:v>
       </x:c>
+      <x:c r="L75"/>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="67" t="str">
@@ -7613,6 +7992,7 @@
       <x:c r="K76" s="67" t="str">
         <x:v>employees.employee_code</x:v>
       </x:c>
+      <x:c r="L76"/>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="67" t="str">
@@ -7648,6 +8028,7 @@
       <x:c r="K77" s="67" t="str">
         <x:v>employees.name</x:v>
       </x:c>
+      <x:c r="L77"/>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
       <x:c r="A78" s="67" t="str">
@@ -7666,7 +8047,7 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F78" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G78" s="67" t="str">
         <x:v>最大100</x:v>
@@ -7675,7 +8056,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I78" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J78" s="67" t="str">
         <x:v>氏名Kana</x:v>
@@ -7683,6 +8064,7 @@
       <x:c r="K78" s="67" t="str">
         <x:v>employees.name_kana</x:v>
       </x:c>
+      <x:c r="L78"/>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="67" t="str">
@@ -7718,6 +8100,7 @@
       <x:c r="K79" s="67" t="str">
         <x:v>employees.email</x:v>
       </x:c>
+      <x:c r="L79"/>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="67" t="str">
@@ -7736,7 +8119,7 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F80" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G80" s="67" t="str">
         <x:v>最大20</x:v>
@@ -7745,7 +8128,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I80" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J80" s="67" t="str">
         <x:v>電話番号</x:v>
@@ -7753,6 +8136,7 @@
       <x:c r="K80" s="67" t="str">
         <x:v>employees.phone_number</x:v>
       </x:c>
+      <x:c r="L80"/>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="67" t="str">
@@ -7788,6 +8172,7 @@
       <x:c r="K81" s="67" t="str">
         <x:v>employees.department_id</x:v>
       </x:c>
+      <x:c r="L81"/>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="67" t="str">
@@ -7823,6 +8208,7 @@
       <x:c r="K82" s="67" t="str">
         <x:v>employees.position</x:v>
       </x:c>
+      <x:c r="L82"/>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="67" t="str">
@@ -7858,6 +8244,7 @@
       <x:c r="K83" s="67" t="str">
         <x:v>employees.joined_date</x:v>
       </x:c>
+      <x:c r="L83"/>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="67" t="str">
@@ -7876,7 +8263,7 @@
         <x:v>Long</x:v>
       </x:c>
       <x:c r="F84" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G84" s="67" t="str">
         <x:v>-</x:v>
@@ -7885,7 +8272,7 @@
         <x:v>int64</x:v>
       </x:c>
       <x:c r="I84" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J84" s="67" t="str">
         <x:v>上長/管理者ID</x:v>
@@ -7893,6 +8280,7 @@
       <x:c r="K84" s="67" t="str">
         <x:v>employees.manager_id</x:v>
       </x:c>
+      <x:c r="L84"/>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="67" t="str">
@@ -7928,8 +8316,9 @@
       <x:c r="K85" s="67" t="str">
         <x:v>users.username</x:v>
       </x:c>
-    </x:row>
-    <x:row r="86" ht="15" hidden="0" customHeight="1">
+      <x:c r="L85"/>
+    </x:row>
+    <x:row r="86" ht="40" hidden="0" customHeight="1">
       <x:c r="A86" s="67" t="str">
         <x:v>API-EMP-003</x:v>
       </x:c>
@@ -7958,11 +8347,12 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J86" s="67" t="str">
-        <x:v>Role ID一覧</x:v>
+        <x:v>有効Roleのみ、重複なし、内蔵Roleを1つ以上。02／09。</x:v>
       </x:c>
       <x:c r="K86" s="67" t="str">
         <x:v>COLLECTION INPUT: roleIds[] → user_roles.role_id for created user</x:v>
       </x:c>
+      <x:c r="L86" s="241"/>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="67" t="str">
@@ -7981,7 +8371,7 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F87" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G87" s="67" t="str">
         <x:v>最大1000</x:v>
@@ -7990,7 +8380,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I87" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J87" s="67" t="str">
         <x:v>備考</x:v>
@@ -7998,6 +8388,7 @@
       <x:c r="K87" s="67" t="str">
         <x:v>employees.remark</x:v>
       </x:c>
+      <x:c r="L87"/>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="67" t="str">
@@ -8033,6 +8424,7 @@
       <x:c r="K88" s="67" t="str">
         <x:v>HTTP Header</x:v>
       </x:c>
+      <x:c r="L88"/>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
       <x:c r="A89" s="67" t="str">
@@ -8068,6 +8460,7 @@
       <x:c r="K89" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L89"/>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
       <x:c r="A90" s="67" t="str">
@@ -8103,6 +8496,7 @@
       <x:c r="K90" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L90"/>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
       <x:c r="A91" s="67" t="str">
@@ -8138,6 +8532,7 @@
       <x:c r="K91" s="67" t="str">
         <x:v>Response DTO</x:v>
       </x:c>
+      <x:c r="L91"/>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
       <x:c r="A92" s="67" t="str">
@@ -8173,6 +8568,7 @@
       <x:c r="K92" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L92"/>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
       <x:c r="A93" s="67" t="str">
@@ -8208,6 +8604,7 @@
       <x:c r="K93" s="67" t="str">
         <x:v>Log traceId</x:v>
       </x:c>
+      <x:c r="L93"/>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
       <x:c r="A94" s="67" t="str">
@@ -8243,6 +8640,7 @@
       <x:c r="K94" s="67" t="str">
         <x:v>employees.id</x:v>
       </x:c>
+      <x:c r="L94"/>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
       <x:c r="A95" s="67" t="str">
@@ -8278,8 +8676,9 @@
       <x:c r="K95" s="67" t="str">
         <x:v>employees.employee_code</x:v>
       </x:c>
-    </x:row>
-    <x:row r="96" ht="15" hidden="0" customHeight="1">
+      <x:c r="L95"/>
+    </x:row>
+    <x:row r="96" ht="40" hidden="0" customHeight="1">
       <x:c r="A96" s="67" t="str">
         <x:v>API-EMP-003</x:v>
       </x:c>
@@ -8305,14 +8704,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I96" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J96" s="67" t="str">
-        <x:v>temporaryPassword</x:v>
+        <x:v>初回成功のみ一時Password。冪等再送はNull（処理済）。BR-API-002。</x:v>
       </x:c>
       <x:c r="K96" s="67" t="str">
         <x:v>Service生成（一時Password）</x:v>
       </x:c>
+      <x:c r="L96" s="241"/>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="67" t="str">
@@ -8348,6 +8748,7 @@
       <x:c r="K97" s="67" t="str">
         <x:v>employees.id</x:v>
       </x:c>
+      <x:c r="L97"/>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
       <x:c r="A98" s="67" t="str">
@@ -8383,6 +8784,7 @@
       <x:c r="K98" s="67" t="str">
         <x:v>employees.name</x:v>
       </x:c>
+      <x:c r="L98"/>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
       <x:c r="A99" s="67" t="str">
@@ -8418,6 +8820,7 @@
       <x:c r="K99" s="67" t="str">
         <x:v>employees.name_kana</x:v>
       </x:c>
+      <x:c r="L99"/>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
       <x:c r="A100" s="67" t="str">
@@ -8453,6 +8856,7 @@
       <x:c r="K100" s="67" t="str">
         <x:v>employees.email</x:v>
       </x:c>
+      <x:c r="L100"/>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
       <x:c r="A101" s="67" t="str">
@@ -8488,6 +8892,7 @@
       <x:c r="K101" s="67" t="str">
         <x:v>employees.phone_number</x:v>
       </x:c>
+      <x:c r="L101"/>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
       <x:c r="A102" s="67" t="str">
@@ -8523,6 +8928,7 @@
       <x:c r="K102" s="67" t="str">
         <x:v>employees.department_id</x:v>
       </x:c>
+      <x:c r="L102"/>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
       <x:c r="A103" s="67" t="str">
@@ -8558,6 +8964,7 @@
       <x:c r="K103" s="67" t="str">
         <x:v>employees.position</x:v>
       </x:c>
+      <x:c r="L103"/>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
       <x:c r="A104" s="67" t="str">
@@ -8593,6 +9000,7 @@
       <x:c r="K104" s="67" t="str">
         <x:v>employees.manager_id</x:v>
       </x:c>
+      <x:c r="L104"/>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
       <x:c r="A105" s="67"/>
@@ -8606,6 +9014,7 @@
       <x:c r="I105" s="67"/>
       <x:c r="J105" s="67"/>
       <x:c r="K105" s="67"/>
+      <x:c r="L105"/>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
       <x:c r="A106" s="67"/>
@@ -8619,6 +9028,7 @@
       <x:c r="I106" s="67"/>
       <x:c r="J106" s="67"/>
       <x:c r="K106" s="67"/>
+      <x:c r="L106"/>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
       <x:c r="A107" s="67" t="str">
@@ -8654,6 +9064,7 @@
       <x:c r="K107" s="67" t="str">
         <x:v>employees.remark</x:v>
       </x:c>
+      <x:c r="L107"/>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
       <x:c r="A108" s="67" t="str">
@@ -8689,6 +9100,7 @@
       <x:c r="K108" s="67" t="str">
         <x:v>employees.version</x:v>
       </x:c>
+      <x:c r="L108"/>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
       <x:c r="A109" s="67" t="str">
@@ -8724,6 +9136,7 @@
       <x:c r="K109" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L109"/>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
       <x:c r="A110" s="67" t="str">
@@ -8759,6 +9172,7 @@
       <x:c r="K110" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L110"/>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
       <x:c r="A111" s="67" t="str">
@@ -8794,6 +9208,7 @@
       <x:c r="K111" s="67" t="str">
         <x:v>Response DTO</x:v>
       </x:c>
+      <x:c r="L111"/>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
       <x:c r="A112" s="67" t="str">
@@ -8829,6 +9244,7 @@
       <x:c r="K112" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L112"/>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
       <x:c r="A113" s="67" t="str">
@@ -8864,6 +9280,7 @@
       <x:c r="K113" s="67" t="str">
         <x:v>Log traceId</x:v>
       </x:c>
+      <x:c r="L113"/>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
       <x:c r="A114" s="67" t="str">
@@ -8899,6 +9316,7 @@
       <x:c r="K114" s="67" t="str">
         <x:v>employees.id</x:v>
       </x:c>
+      <x:c r="L114"/>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
       <x:c r="A115" s="67" t="str">
@@ -8934,6 +9352,7 @@
       <x:c r="K115" s="67" t="str">
         <x:v>employees.version</x:v>
       </x:c>
+      <x:c r="L115"/>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
       <x:c r="A116" s="67" t="str">
@@ -8969,6 +9388,7 @@
       <x:c r="K116" s="67" t="str">
         <x:v>employees.id</x:v>
       </x:c>
+      <x:c r="L116"/>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
       <x:c r="A117" s="67" t="str">
@@ -9004,6 +9424,7 @@
       <x:c r="K117" s="67" t="str">
         <x:v>employees.employment_status</x:v>
       </x:c>
+      <x:c r="L117"/>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
       <x:c r="A118" s="67" t="str">
@@ -9039,6 +9460,7 @@
       <x:c r="K118" s="67" t="str">
         <x:v>employees.left_date</x:v>
       </x:c>
+      <x:c r="L118"/>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
       <x:c r="A119" s="67" t="str">
@@ -9057,7 +9479,7 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F119" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>条件必須</x:v>
       </x:c>
       <x:c r="G119" s="67" t="str">
         <x:v>-</x:v>
@@ -9069,11 +9491,12 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J119" s="67" t="str">
-        <x:v>未完了Task存在時必須</x:v>
+        <x:v>未完了Task&gt;0の場合必須。REASSIGN/CANCEL</x:v>
       </x:c>
       <x:c r="K119" s="67" t="str">
         <x:v>退職処理方針（Service入力）</x:v>
       </x:c>
+      <x:c r="L119"/>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
       <x:c r="A120" s="67" t="str">
@@ -9109,6 +9532,7 @@
       <x:c r="K120" s="67" t="str">
         <x:v>employees.id（在籍社員、対象社員以外）</x:v>
       </x:c>
+      <x:c r="L120"/>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
       <x:c r="A121" s="67" t="str">
@@ -9144,6 +9568,7 @@
       <x:c r="K121" s="67" t="str">
         <x:v>employees.version</x:v>
       </x:c>
+      <x:c r="L121"/>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
       <x:c r="A122" s="67" t="str">
@@ -9179,6 +9604,7 @@
       <x:c r="K122" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L122"/>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
       <x:c r="A123" s="67" t="str">
@@ -9214,6 +9640,7 @@
       <x:c r="K123" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L123"/>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
       <x:c r="A124" s="67" t="str">
@@ -9249,6 +9676,7 @@
       <x:c r="K124" s="67" t="str">
         <x:v>Response DTO</x:v>
       </x:c>
+      <x:c r="L124"/>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
       <x:c r="A125" s="67" t="str">
@@ -9284,6 +9712,7 @@
       <x:c r="K125" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L125"/>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
       <x:c r="A126" s="67" t="str">
@@ -9319,6 +9748,7 @@
       <x:c r="K126" s="67" t="str">
         <x:v>Log traceId</x:v>
       </x:c>
+      <x:c r="L126"/>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
       <x:c r="A127" s="67" t="str">
@@ -9354,6 +9784,7 @@
       <x:c r="K127" s="67" t="str">
         <x:v>employees.id</x:v>
       </x:c>
+      <x:c r="L127"/>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
       <x:c r="A128" s="67" t="str">
@@ -9389,6 +9820,7 @@
       <x:c r="K128" s="67" t="str">
         <x:v>employees.employment_status</x:v>
       </x:c>
+      <x:c r="L128"/>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
       <x:c r="A129" s="67" t="str">
@@ -9424,6 +9856,7 @@
       <x:c r="K129" s="67" t="str">
         <x:v>employees.version</x:v>
       </x:c>
+      <x:c r="L129"/>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
       <x:c r="A130" s="67" t="str">
@@ -9459,6 +9892,7 @@
       <x:c r="K130" s="67" t="str">
         <x:v>物理File + Metadata</x:v>
       </x:c>
+      <x:c r="L130"/>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
       <x:c r="A131" s="67" t="str">
@@ -9494,6 +9928,7 @@
       <x:c r="K131" s="67" t="str">
         <x:v>HTTP Header</x:v>
       </x:c>
+      <x:c r="L131"/>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
       <x:c r="A132" s="67" t="str">
@@ -9529,6 +9964,7 @@
       <x:c r="K132" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L132"/>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
       <x:c r="A133" s="67" t="str">
@@ -9564,6 +10000,7 @@
       <x:c r="K133" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L133"/>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
       <x:c r="A134" s="67" t="str">
@@ -9599,6 +10036,7 @@
       <x:c r="K134" s="67" t="str">
         <x:v>Response DTO</x:v>
       </x:c>
+      <x:c r="L134"/>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
       <x:c r="A135" s="67" t="str">
@@ -9634,6 +10072,7 @@
       <x:c r="K135" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L135"/>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
       <x:c r="A136" s="67" t="str">
@@ -9669,6 +10108,7 @@
       <x:c r="K136" s="67" t="str">
         <x:v>Log traceId</x:v>
       </x:c>
+      <x:c r="L136"/>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
       <x:c r="A137" s="67" t="str">
@@ -9704,6 +10144,7 @@
       <x:c r="K137" s="67" t="str">
         <x:v>取込処理集計</x:v>
       </x:c>
+      <x:c r="L137"/>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
       <x:c r="A138" s="67" t="str">
@@ -9739,6 +10180,7 @@
       <x:c r="K138" s="67" t="str">
         <x:v>取込処理集計</x:v>
       </x:c>
+      <x:c r="L138"/>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
       <x:c r="A139" s="67" t="str">
@@ -9774,6 +10216,7 @@
       <x:c r="K139" s="67" t="str">
         <x:v>取込処理集計</x:v>
       </x:c>
+      <x:c r="L139"/>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
       <x:c r="A140" s="67" t="str">
@@ -9804,11 +10247,12 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J140" s="67" t="str">
-        <x:v>errors</x:v>
+        <x:v>行別Error。0件可</x:v>
       </x:c>
       <x:c r="K140" s="67" t="str">
         <x:v>取込処理結果（行別Error）</x:v>
       </x:c>
+      <x:c r="L140"/>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
       <x:c r="A141" s="67" t="str">
@@ -9824,7 +10268,7 @@
         <x:v>response.body.data.errors[].row</x:v>
       </x:c>
       <x:c r="E141" s="67" t="str">
-        <x:v>String</x:v>
+        <x:v>Integer</x:v>
       </x:c>
       <x:c r="F141" s="67" t="str">
         <x:v>必須</x:v>
@@ -9833,17 +10277,18 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="H141" s="67" t="str">
-        <x:v>-</x:v>
+        <x:v>int32</x:v>
       </x:c>
       <x:c r="I141" s="67" t="str">
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J141" s="67" t="str">
-        <x:v>row</x:v>
+        <x:v>Excel行番号（Header=1、Dataは2行目以降）。File全体エラーはこの配列を使用せず共通Error Response。</x:v>
       </x:c>
       <x:c r="K141" s="67" t="str">
         <x:v>取込File行番号</x:v>
       </x:c>
+      <x:c r="L141"/>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
       <x:c r="A142" s="67" t="str">
@@ -9879,6 +10324,7 @@
       <x:c r="K142" s="67" t="str">
         <x:v>取込処理結果（項目名）</x:v>
       </x:c>
+      <x:c r="L142"/>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
       <x:c r="A143" s="67" t="str">
@@ -9909,11 +10355,12 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J143" s="67" t="str">
-        <x:v>code</x:v>
+        <x:v>行単位Error Code（EMP-4001等）。社員番号ではない。</x:v>
       </x:c>
       <x:c r="K143" s="67" t="str">
-        <x:v>employees.employee_code</x:v>
-      </x:c>
+        <x:v>取込処理の検証結果Code</x:v>
+      </x:c>
+      <x:c r="L143"/>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
       <x:c r="A144" s="67" t="str">
@@ -9949,6 +10396,7 @@
       <x:c r="K144" s="67" t="str">
         <x:v>取込処理結果（Message）</x:v>
       </x:c>
+      <x:c r="L144"/>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
       <x:c r="A145" s="67" t="str">
@@ -9984,6 +10432,7 @@
       <x:c r="K145" s="67" t="str">
         <x:v>employees.employee_code</x:v>
       </x:c>
+      <x:c r="L145"/>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
       <x:c r="A146" s="67" t="str">
@@ -10019,6 +10468,7 @@
       <x:c r="K146" s="67" t="str">
         <x:v>employees.name</x:v>
       </x:c>
+      <x:c r="L146"/>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
       <x:c r="A147" s="67" t="str">
@@ -10054,6 +10504,7 @@
       <x:c r="K147" s="67" t="str">
         <x:v>employees.email</x:v>
       </x:c>
+      <x:c r="L147"/>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
       <x:c r="A148" s="67" t="str">
@@ -10089,6 +10540,7 @@
       <x:c r="K148" s="67" t="str">
         <x:v>employees.department_id</x:v>
       </x:c>
+      <x:c r="L148"/>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
       <x:c r="A149" s="67" t="str">
@@ -10124,6 +10576,7 @@
       <x:c r="K149" s="67" t="str">
         <x:v>検索条件（employees.joined_date From）</x:v>
       </x:c>
+      <x:c r="L149"/>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
       <x:c r="A150" s="67" t="str">
@@ -10159,6 +10612,7 @@
       <x:c r="K150" s="67" t="str">
         <x:v>検索条件（employees.joined_date To）</x:v>
       </x:c>
+      <x:c r="L150"/>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
       <x:c r="A151" s="67" t="str">
@@ -10194,6 +10648,7 @@
       <x:c r="K151" s="67" t="str">
         <x:v>employees.employment_status</x:v>
       </x:c>
+      <x:c r="L151"/>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
       <x:c r="A152" s="67" t="str">
@@ -10229,6 +10684,7 @@
       <x:c r="K152" s="67" t="str">
         <x:v>検索条件</x:v>
       </x:c>
+      <x:c r="L152"/>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
       <x:c r="A153" s="67" t="str">
@@ -10264,6 +10720,7 @@
       <x:c r="K153" s="67" t="str">
         <x:v>検索条件</x:v>
       </x:c>
+      <x:c r="L153"/>
     </x:row>
     <x:row r="154" ht="24" hidden="0" customHeight="1">
       <x:c r="A154" s="67" t="str">
@@ -10299,6 +10756,7 @@
       <x:c r="K154" s="67" t="str">
         <x:v>検索条件</x:v>
       </x:c>
+      <x:c r="L154"/>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
       <x:c r="A155" s="67" t="str">
@@ -10308,7 +10766,7 @@
         <x:v>Response</x:v>
       </x:c>
       <x:c r="C155" s="67" t="str">
-        <x:v>body</x:v>
+        <x:v>header</x:v>
       </x:c>
       <x:c r="D155" s="67" t="str">
         <x:v>response.header.Content-Type</x:v>
@@ -10334,6 +10792,7 @@
       <x:c r="K155" s="67" t="str">
         <x:v>HTTP Header</x:v>
       </x:c>
+      <x:c r="L155"/>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
       <x:c r="A156" s="67" t="str">
@@ -10343,7 +10802,7 @@
         <x:v>Response</x:v>
       </x:c>
       <x:c r="C156" s="67" t="str">
-        <x:v>body</x:v>
+        <x:v>header</x:v>
       </x:c>
       <x:c r="D156" s="67" t="str">
         <x:v>response.header.Content-Disposition</x:v>
@@ -10369,6 +10828,7 @@
       <x:c r="K156" s="67" t="str">
         <x:v>HTTP Header</x:v>
       </x:c>
+      <x:c r="L156"/>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
       <x:c r="A157" s="67" t="str">
@@ -10404,6 +10864,7 @@
       <x:c r="K157" s="67" t="str">
         <x:v>物理File</x:v>
       </x:c>
+      <x:c r="L157"/>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
       <x:c r="A158" s="67" t="str">
@@ -10439,6 +10900,7 @@
       <x:c r="K158" s="67" t="str">
         <x:v>検索条件</x:v>
       </x:c>
+      <x:c r="L158"/>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
       <x:c r="A159" s="67" t="str">
@@ -10474,6 +10936,7 @@
       <x:c r="K159" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L159"/>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
       <x:c r="A160" s="67" t="str">
@@ -10509,6 +10972,7 @@
       <x:c r="K160" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L160"/>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
       <x:c r="A161" s="67" t="str">
@@ -10544,6 +11008,7 @@
       <x:c r="K161" s="67" t="str">
         <x:v>Response DTO</x:v>
       </x:c>
+      <x:c r="L161"/>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
       <x:c r="A162" s="67" t="str">
@@ -10579,6 +11044,7 @@
       <x:c r="K162" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L162"/>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
       <x:c r="A163" s="67" t="str">
@@ -10614,6 +11080,7 @@
       <x:c r="K163" s="67" t="str">
         <x:v>Log traceId</x:v>
       </x:c>
+      <x:c r="L163"/>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
       <x:c r="A164" s="67" t="str">
@@ -10649,6 +11116,7 @@
       <x:c r="K164" s="67" t="str">
         <x:v>departments</x:v>
       </x:c>
+      <x:c r="L164"/>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
       <x:c r="A165" s="67" t="str">
@@ -10684,6 +11152,7 @@
       <x:c r="K165" s="67" t="str">
         <x:v>departments.id</x:v>
       </x:c>
+      <x:c r="L165"/>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
       <x:c r="A166" s="67" t="str">
@@ -10705,7 +11174,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G166" s="67" t="str">
-        <x:v>最大20</x:v>
+        <x:v>最大30</x:v>
       </x:c>
       <x:c r="H166" s="67" t="str">
         <x:v>-</x:v>
@@ -10719,6 +11188,7 @@
       <x:c r="K166" s="67" t="str">
         <x:v>departments.department_code</x:v>
       </x:c>
+      <x:c r="L166"/>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
       <x:c r="A167" s="67" t="str">
@@ -10754,6 +11224,7 @@
       <x:c r="K167" s="67" t="str">
         <x:v>departments.department_name</x:v>
       </x:c>
+      <x:c r="L167"/>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
       <x:c r="A168" s="67" t="str">
@@ -10789,6 +11260,7 @@
       <x:c r="K168" s="67" t="str">
         <x:v>departments.parent_id</x:v>
       </x:c>
+      <x:c r="L168"/>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
       <x:c r="A169" s="67" t="str">
@@ -10824,6 +11296,7 @@
       <x:c r="K169" s="67" t="str">
         <x:v>departments.manager_id</x:v>
       </x:c>
+      <x:c r="L169"/>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
       <x:c r="A170" s="67" t="str">
@@ -10859,6 +11332,7 @@
       <x:c r="K170" s="67" t="str">
         <x:v>departments.display_order</x:v>
       </x:c>
+      <x:c r="L170"/>
     </x:row>
     <x:row r="171" ht="24" hidden="0" customHeight="1">
       <x:c r="A171" s="67" t="str">
@@ -10894,6 +11368,7 @@
       <x:c r="K171" s="67" t="str">
         <x:v>departments.status</x:v>
       </x:c>
+      <x:c r="L171"/>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
       <x:c r="A172" s="67" t="str">
@@ -10929,6 +11404,7 @@
       <x:c r="K172" s="67" t="str">
         <x:v>HIERARCHY: departments.parent_id = parent departments.id; child rows mapped to Object[]</x:v>
       </x:c>
+      <x:c r="L172"/>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
       <x:c r="A173" s="67" t="str">
@@ -10964,6 +11440,7 @@
       <x:c r="K173" s="67" t="str">
         <x:v>departments.id</x:v>
       </x:c>
+      <x:c r="L173"/>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
       <x:c r="A174" s="67" t="str">
@@ -10985,7 +11462,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G174" s="67" t="str">
-        <x:v>最大20</x:v>
+        <x:v>最大30</x:v>
       </x:c>
       <x:c r="H174" s="67" t="str">
         <x:v>-</x:v>
@@ -10999,6 +11476,7 @@
       <x:c r="K174" s="67" t="str">
         <x:v>departments.department_code</x:v>
       </x:c>
+      <x:c r="L174"/>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
       <x:c r="A175" s="67" t="str">
@@ -11034,6 +11512,7 @@
       <x:c r="K175" s="67" t="str">
         <x:v>departments.department_name</x:v>
       </x:c>
+      <x:c r="L175"/>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
       <x:c r="A176" s="67" t="str">
@@ -11069,6 +11548,7 @@
       <x:c r="K176" s="67" t="str">
         <x:v>departments.manager_id</x:v>
       </x:c>
+      <x:c r="L176"/>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
       <x:c r="A177" s="67" t="str">
@@ -11104,6 +11584,7 @@
       <x:c r="K177" s="67" t="str">
         <x:v>departments.display_order</x:v>
       </x:c>
+      <x:c r="L177"/>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
       <x:c r="A178" s="67" t="str">
@@ -11139,6 +11620,7 @@
       <x:c r="K178" s="67" t="str">
         <x:v>departments.status</x:v>
       </x:c>
+      <x:c r="L178"/>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
       <x:c r="A179" s="67" t="str">
@@ -11174,6 +11656,7 @@
       <x:c r="K179" s="67" t="str">
         <x:v>AGGREGATE: COUNT(child.id) WHERE child.parent_id = departments.id</x:v>
       </x:c>
+      <x:c r="L179"/>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
       <x:c r="A180" s="67" t="str">
@@ -11209,6 +11692,7 @@
       <x:c r="K180" s="67" t="str">
         <x:v>departments.version</x:v>
       </x:c>
+      <x:c r="L180"/>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
       <x:c r="A181" s="67" t="str">
@@ -11244,6 +11728,7 @@
       <x:c r="K181" s="67" t="str">
         <x:v>departments.id</x:v>
       </x:c>
+      <x:c r="L181"/>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
       <x:c r="A182" s="67" t="str">
@@ -11279,6 +11764,7 @@
       <x:c r="K182" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L182"/>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
       <x:c r="A183" s="67" t="str">
@@ -11314,6 +11800,7 @@
       <x:c r="K183" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L183"/>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
       <x:c r="A184" s="67" t="str">
@@ -11349,6 +11836,7 @@
       <x:c r="K184" s="67" t="str">
         <x:v>Response DTO</x:v>
       </x:c>
+      <x:c r="L184"/>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
       <x:c r="A185" s="67" t="str">
@@ -11384,6 +11872,7 @@
       <x:c r="K185" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L185"/>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
       <x:c r="A186" s="67" t="str">
@@ -11419,6 +11908,7 @@
       <x:c r="K186" s="67" t="str">
         <x:v>Log traceId</x:v>
       </x:c>
+      <x:c r="L186"/>
     </x:row>
     <x:row r="187" ht="15" hidden="0" customHeight="1">
       <x:c r="A187" s="67" t="str">
@@ -11454,6 +11944,7 @@
       <x:c r="K187" s="67" t="str">
         <x:v>departments.id</x:v>
       </x:c>
+      <x:c r="L187"/>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
       <x:c r="A188" s="67" t="str">
@@ -11489,6 +11980,7 @@
       <x:c r="K188" s="67" t="str">
         <x:v>departments.department_code</x:v>
       </x:c>
+      <x:c r="L188"/>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
       <x:c r="A189" s="67" t="str">
@@ -11524,6 +12016,7 @@
       <x:c r="K189" s="67" t="str">
         <x:v>departments.department_name</x:v>
       </x:c>
+      <x:c r="L189"/>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
       <x:c r="A190" s="67" t="str">
@@ -11551,14 +12044,15 @@
         <x:v>int64</x:v>
       </x:c>
       <x:c r="I190" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J190" s="67" t="str">
-        <x:v>parentId</x:v>
+        <x:v>親部門ID。RootはNull（16／28 BR-DEPT-005）。</x:v>
       </x:c>
       <x:c r="K190" s="67" t="str">
         <x:v>departments.parent_id</x:v>
       </x:c>
+      <x:c r="L190"/>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
       <x:c r="A191" s="67" t="str">
@@ -11586,14 +12080,15 @@
         <x:v>int64</x:v>
       </x:c>
       <x:c r="I191" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J191" s="67" t="str">
-        <x:v>上長/管理者ID</x:v>
+        <x:v>部門責任者の社員ID。未設定はNull（05／15_画面項目定義 managerId、15／07 departments.manager_id）。</x:v>
       </x:c>
       <x:c r="K191" s="67" t="str">
         <x:v>departments.manager_id</x:v>
       </x:c>
+      <x:c r="L191"/>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
       <x:c r="A192" s="67" t="str">
@@ -11629,6 +12124,7 @@
       <x:c r="K192" s="67" t="str">
         <x:v>departments.display_order</x:v>
       </x:c>
+      <x:c r="L192"/>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
       <x:c r="A193" s="67" t="str">
@@ -11664,6 +12160,7 @@
       <x:c r="K193" s="67" t="str">
         <x:v>departments.status</x:v>
       </x:c>
+      <x:c r="L193"/>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
       <x:c r="A194" s="67" t="str">
@@ -11699,6 +12196,7 @@
       <x:c r="K194" s="67" t="str">
         <x:v>departments.version</x:v>
       </x:c>
+      <x:c r="L194"/>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
       <x:c r="A195" s="67" t="str">
@@ -11720,7 +12218,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G195" s="67" t="str">
-        <x:v>最大20</x:v>
+        <x:v>最大30</x:v>
       </x:c>
       <x:c r="H195" s="67" t="str">
         <x:v>-</x:v>
@@ -11734,6 +12232,7 @@
       <x:c r="K195" s="67" t="str">
         <x:v>departments.department_code</x:v>
       </x:c>
+      <x:c r="L195"/>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
       <x:c r="A196" s="67" t="str">
@@ -11769,6 +12268,7 @@
       <x:c r="K196" s="67" t="str">
         <x:v>departments.department_name</x:v>
       </x:c>
+      <x:c r="L196"/>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
       <x:c r="A197" s="67" t="str">
@@ -11787,7 +12287,7 @@
         <x:v>Long</x:v>
       </x:c>
       <x:c r="F197" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G197" s="67" t="str">
         <x:v>-</x:v>
@@ -11796,7 +12296,7 @@
         <x:v>int64</x:v>
       </x:c>
       <x:c r="I197" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J197" s="67" t="str">
         <x:v>parentId</x:v>
@@ -11804,6 +12304,7 @@
       <x:c r="K197" s="67" t="str">
         <x:v>departments.parent_id</x:v>
       </x:c>
+      <x:c r="L197"/>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
       <x:c r="A198" s="67" t="str">
@@ -11822,7 +12323,7 @@
         <x:v>Long</x:v>
       </x:c>
       <x:c r="F198" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G198" s="67" t="str">
         <x:v>-</x:v>
@@ -11831,7 +12332,7 @@
         <x:v>int64</x:v>
       </x:c>
       <x:c r="I198" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J198" s="67" t="str">
         <x:v>上長/管理者ID</x:v>
@@ -11839,6 +12340,7 @@
       <x:c r="K198" s="67" t="str">
         <x:v>departments.manager_id</x:v>
       </x:c>
+      <x:c r="L198"/>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
       <x:c r="A199" s="67" t="str">
@@ -11874,6 +12376,7 @@
       <x:c r="K199" s="67" t="str">
         <x:v>departments.display_order</x:v>
       </x:c>
+      <x:c r="L199"/>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
       <x:c r="A200" s="67" t="str">
@@ -11909,6 +12412,7 @@
       <x:c r="K200" s="67" t="str">
         <x:v>departments.status</x:v>
       </x:c>
+      <x:c r="L200"/>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
       <x:c r="A201" s="67" t="str">
@@ -11944,6 +12448,7 @@
       <x:c r="K201" s="67" t="str">
         <x:v>HTTP Header</x:v>
       </x:c>
+      <x:c r="L201"/>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
       <x:c r="A202" s="67" t="str">
@@ -11979,6 +12484,7 @@
       <x:c r="K202" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L202"/>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
       <x:c r="A203" s="67" t="str">
@@ -12014,6 +12520,7 @@
       <x:c r="K203" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L203"/>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
       <x:c r="A204" s="67" t="str">
@@ -12049,6 +12556,7 @@
       <x:c r="K204" s="67" t="str">
         <x:v>Response DTO</x:v>
       </x:c>
+      <x:c r="L204"/>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
       <x:c r="A205" s="67" t="str">
@@ -12084,6 +12592,7 @@
       <x:c r="K205" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L205"/>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
       <x:c r="A206" s="67" t="str">
@@ -12119,6 +12628,7 @@
       <x:c r="K206" s="67" t="str">
         <x:v>Log traceId</x:v>
       </x:c>
+      <x:c r="L206"/>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
       <x:c r="A207" s="67" t="str">
@@ -12154,6 +12664,7 @@
       <x:c r="K207" s="67" t="str">
         <x:v>departments.id</x:v>
       </x:c>
+      <x:c r="L207"/>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
       <x:c r="A208" s="67" t="str">
@@ -12189,6 +12700,7 @@
       <x:c r="K208" s="67" t="str">
         <x:v>departments.version</x:v>
       </x:c>
+      <x:c r="L208"/>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
       <x:c r="A209" s="67" t="str">
@@ -12224,6 +12736,7 @@
       <x:c r="K209" s="67" t="str">
         <x:v>departments.id</x:v>
       </x:c>
+      <x:c r="L209"/>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
       <x:c r="A210" s="67" t="str">
@@ -12259,6 +12772,7 @@
       <x:c r="K210" s="67" t="str">
         <x:v>departments.department_name</x:v>
       </x:c>
+      <x:c r="L210"/>
     </x:row>
     <x:row r="211" ht="15" hidden="0" customHeight="1">
       <x:c r="A211" s="67" t="str">
@@ -12277,7 +12791,7 @@
         <x:v>Long</x:v>
       </x:c>
       <x:c r="F211" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G211" s="67" t="str">
         <x:v>-</x:v>
@@ -12286,7 +12800,7 @@
         <x:v>int64</x:v>
       </x:c>
       <x:c r="I211" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J211" s="67" t="str">
         <x:v>parentId</x:v>
@@ -12294,6 +12808,7 @@
       <x:c r="K211" s="67" t="str">
         <x:v>departments.parent_id</x:v>
       </x:c>
+      <x:c r="L211"/>
     </x:row>
     <x:row r="212" ht="15" hidden="0" customHeight="1">
       <x:c r="A212" s="67" t="str">
@@ -12312,7 +12827,7 @@
         <x:v>Long</x:v>
       </x:c>
       <x:c r="F212" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G212" s="67" t="str">
         <x:v>-</x:v>
@@ -12321,7 +12836,7 @@
         <x:v>int64</x:v>
       </x:c>
       <x:c r="I212" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J212" s="67" t="str">
         <x:v>上長/管理者ID</x:v>
@@ -12329,6 +12844,7 @@
       <x:c r="K212" s="67" t="str">
         <x:v>departments.manager_id</x:v>
       </x:c>
+      <x:c r="L212"/>
     </x:row>
     <x:row r="213" ht="15" hidden="0" customHeight="1">
       <x:c r="A213" s="67" t="str">
@@ -12364,6 +12880,7 @@
       <x:c r="K213" s="67" t="str">
         <x:v>departments.display_order</x:v>
       </x:c>
+      <x:c r="L213"/>
     </x:row>
     <x:row r="214" ht="15" hidden="0" customHeight="1">
       <x:c r="A214" s="67" t="str">
@@ -12399,6 +12916,7 @@
       <x:c r="K214" s="67" t="str">
         <x:v>departments.status</x:v>
       </x:c>
+      <x:c r="L214"/>
     </x:row>
     <x:row r="215" ht="15" hidden="0" customHeight="1">
       <x:c r="A215" s="67" t="str">
@@ -12434,6 +12952,7 @@
       <x:c r="K215" s="67" t="str">
         <x:v>departments.version</x:v>
       </x:c>
+      <x:c r="L215"/>
     </x:row>
     <x:row r="216" ht="15" hidden="0" customHeight="1">
       <x:c r="A216" s="67" t="str">
@@ -12469,6 +12988,7 @@
       <x:c r="K216" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L216"/>
     </x:row>
     <x:row r="217" ht="15" hidden="0" customHeight="1">
       <x:c r="A217" s="67" t="str">
@@ -12504,6 +13024,7 @@
       <x:c r="K217" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L217"/>
     </x:row>
     <x:row r="218" ht="15" hidden="0" customHeight="1">
       <x:c r="A218" s="67" t="str">
@@ -12539,6 +13060,7 @@
       <x:c r="K218" s="67" t="str">
         <x:v>Response DTO</x:v>
       </x:c>
+      <x:c r="L218"/>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="67" t="str">
@@ -12574,6 +13096,7 @@
       <x:c r="K219" s="67" t="str">
         <x:v>共通Response</x:v>
       </x:c>
+      <x:c r="L219"/>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="67" t="str">
@@ -12609,6 +13132,7 @@
       <x:c r="K220" s="67" t="str">
         <x:v>Log traceId</x:v>
       </x:c>
+      <x:c r="L220"/>
     </x:row>
     <x:row r="221" ht="15" hidden="0" customHeight="1">
       <x:c r="A221" s="67" t="str">
@@ -12644,6 +13168,7 @@
       <x:c r="K221" s="67" t="str">
         <x:v>departments.id</x:v>
       </x:c>
+      <x:c r="L221"/>
     </x:row>
     <x:row r="222" ht="15" hidden="0" customHeight="1">
       <x:c r="A222" s="67" t="str">
@@ -12679,6 +13204,7 @@
       <x:c r="K222" s="67" t="str">
         <x:v>departments.version</x:v>
       </x:c>
+      <x:c r="L222"/>
     </x:row>
     <x:row r="223" ht="15" hidden="0" customHeight="1">
       <x:c r="A223" s="67" t="str">
@@ -12714,8 +13240,9 @@
       <x:c r="K223" s="67" t="str">
         <x:v>departments.id</x:v>
       </x:c>
-    </x:row>
-    <x:row r="224" ht="15" hidden="0" customHeight="1">
+      <x:c r="L223"/>
+    </x:row>
+    <x:row r="224" ht="65" hidden="0" customHeight="1">
       <x:c r="A224" s="67" t="str">
         <x:v>API-DEPT-005</x:v>
       </x:c>
@@ -12732,58 +13259,38 @@
         <x:v>Integer</x:v>
       </x:c>
       <x:c r="F224" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="G224" s="67" t="str">
-        <x:v>-</x:v>
+        <x:v>0以上の整数</x:v>
       </x:c>
       <x:c r="H224" s="67" t="str">
         <x:v>int32</x:v>
       </x:c>
       <x:c r="I224" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>不可</x:v>
       </x:c>
       <x:c r="J224" s="67" t="str">
-        <x:v>楽観Lock Version</x:v>
+        <x:v>Version。欠落/Null/形式不正=COMMON-4000、既存対象の不一致=COMMON-4090、削除済/不存在=COMMON-4040。権限確認後に判定。</x:v>
       </x:c>
       <x:c r="K224" s="67" t="str">
         <x:v>departments.version</x:v>
       </x:c>
+      <x:c r="L224"/>
     </x:row>
     <x:row r="225" ht="15" hidden="0" customHeight="1">
-      <x:c r="A225" s="67" t="str">
-        <x:v>API-TASK-009</x:v>
-      </x:c>
-      <x:c r="B225" s="67" t="str">
-        <x:v>Request</x:v>
-      </x:c>
-      <x:c r="C225" s="67" t="str">
-        <x:v>path</x:v>
-      </x:c>
-      <x:c r="D225" s="67" t="str">
-        <x:v>request.path.id</x:v>
-      </x:c>
-      <x:c r="E225" s="67" t="str">
-        <x:v>Long</x:v>
-      </x:c>
-      <x:c r="F225" s="67" t="str">
-        <x:v>必須</x:v>
-      </x:c>
-      <x:c r="G225" s="67" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H225" s="67" t="str">
-        <x:v>int64</x:v>
-      </x:c>
-      <x:c r="I225" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="J225" s="67" t="str">
-        <x:v>Task ID</x:v>
-      </x:c>
-      <x:c r="K225" s="67" t="str">
-        <x:v>tasks.id</x:v>
-      </x:c>
+      <x:c r="A225" s="67"/>
+      <x:c r="B225" s="67"/>
+      <x:c r="C225" s="67"/>
+      <x:c r="D225" s="67"/>
+      <x:c r="E225" s="67"/>
+      <x:c r="F225" s="67"/>
+      <x:c r="G225" s="67"/>
+      <x:c r="H225" s="67"/>
+      <x:c r="I225" s="67"/>
+      <x:c r="J225" s="67"/>
+      <x:c r="K225" s="67"/>
+      <x:c r="L225"/>
     </x:row>
     <x:row r="226" ht="15" hidden="0" customHeight="1">
       <x:c r="A226" t="str">
@@ -12798,11 +13305,11 @@
       <x:c r="D226" t="str">
         <x:v>response.body</x:v>
       </x:c>
-      <x:c r="E226" t="str">
-        <x:v>Null</x:v>
-      </x:c>
-      <x:c r="F226" t="str">
-        <x:v>任意</x:v>
+      <x:c r="E226" s="203" t="str">
+        <x:v>Bodyなし</x:v>
+      </x:c>
+      <x:c r="F226" s="203" t="str">
+        <x:v>送信禁止</x:v>
       </x:c>
       <x:c r="G226" t="str">
         <x:v>-</x:v>
@@ -12810,15 +13317,16 @@
       <x:c r="H226" t="str">
         <x:v>No Content</x:v>
       </x:c>
-      <x:c r="I226" t="str">
-        <x:v>可</x:v>
-      </x:c>
-      <x:c r="J226" t="str">
-        <x:v>Response Bodyなし</x:v>
+      <x:c r="I226" s="203" t="str">
+        <x:v>該当なし</x:v>
+      </x:c>
+      <x:c r="J226" s="203" t="str">
+        <x:v>HTTP 204。JSON null、Envelope、空Objectを送信しない。</x:v>
       </x:c>
       <x:c r="K226" s="203" t="str">
         <x:v>-</x:v>
       </x:c>
+      <x:c r="L226"/>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="186"/>
@@ -12832,11 +13340,10 @@
       <x:c r="I227" s="186"/>
       <x:c r="J227" s="186"/>
       <x:c r="K227" s="204"/>
+      <x:c r="L227"/>
     </x:row>
     <x:row r="228">
-      <x:c r="A228" s="186" t="str">
-        <x:v>JSON Path、型、必須、桁、Enum、Null、DB／生成元を外部契約として固定する。Path IDはDB型BIGINTに合わせLongとする。</x:v>
-      </x:c>
+      <x:c r="A228" s="186" t="str"/>
       <x:c r="B228" s="186"/>
       <x:c r="C228" s="186"/>
       <x:c r="D228" s="186"/>
@@ -12847,26 +13354,517 @@
       <x:c r="I228" s="186"/>
       <x:c r="J228" s="186"/>
       <x:c r="K228" s="186"/>
+      <x:c r="L228"/>
+    </x:row>
+    <x:row r="229" ht="34" customHeight="1">
+      <x:c r="A229" s="203" t="str">
+        <x:v>API-EMP-006</x:v>
+      </x:c>
+      <x:c r="B229" s="203" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C229" s="203" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D229" s="203" t="str">
+        <x:v>response.body.data.successes[]</x:v>
+      </x:c>
+      <x:c r="E229" s="203" t="str">
+        <x:v>Array&lt;Object&gt;</x:v>
+      </x:c>
+      <x:c r="F229" s="203" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G229" s="203" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H229" s="203" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="I229" s="203" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J229" s="203" t="str">
+        <x:v>成功行一覧。0件可</x:v>
+      </x:c>
+      <x:c r="K229" s="203" t="str">
+        <x:v>取込処理結果</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="34" customHeight="1">
+      <x:c r="A230" s="203" t="str">
+        <x:v>API-EMP-006</x:v>
+      </x:c>
+      <x:c r="B230" s="203" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C230" s="203" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D230" s="203" t="str">
+        <x:v>response.body.data.successes[].row</x:v>
+      </x:c>
+      <x:c r="E230" s="203" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="F230" s="203" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G230" s="203" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H230" s="203" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="I230" s="203" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J230" s="203" t="str">
+        <x:v>取込File行番号</x:v>
+      </x:c>
+      <x:c r="K230" s="203" t="str">
+        <x:v>取込処理結果</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="34" customHeight="1">
+      <x:c r="A231" s="203" t="str">
+        <x:v>API-EMP-006</x:v>
+      </x:c>
+      <x:c r="B231" s="203" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C231" s="203" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D231" s="203" t="str">
+        <x:v>response.body.data.successes[].employeeCode</x:v>
+      </x:c>
+      <x:c r="E231" s="203" t="str">
+        <x:v>String</x:v>
+      </x:c>
+      <x:c r="F231" s="203" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G231" s="203" t="str">
+        <x:v>最大20</x:v>
+      </x:c>
+      <x:c r="H231" s="203" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I231" s="203" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J231" s="203" t="str">
+        <x:v>登録社員番号</x:v>
+      </x:c>
+      <x:c r="K231" s="203" t="str">
+        <x:v>employees.employee_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="40" customHeight="1">
+      <x:c r="A232" s="241" t="str">
+        <x:v>API-EMP-006</x:v>
+      </x:c>
+      <x:c r="B232" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C232" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D232" s="241" t="str">
+        <x:v>response.body.data.successes[].temporaryPassword</x:v>
+      </x:c>
+      <x:c r="E232" s="241" t="str">
+        <x:v>String</x:v>
+      </x:c>
+      <x:c r="F232" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G232" s="241" t="str">
+        <x:v>最大64</x:v>
+      </x:c>
+      <x:c r="H232" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I232" s="241" t="str">
+        <x:v>可</x:v>
+      </x:c>
+      <x:c r="J232" s="241" t="str">
+        <x:v>初回成功のみ一時Password。冪等再送はNull（処理済）。BR-API-002。</x:v>
+      </x:c>
+      <x:c r="K232" s="241" t="str">
+        <x:v>Service生成（一時Password）</x:v>
+      </x:c>
+      <x:c r="L232" s="241"/>
+    </x:row>
+    <x:row r="233" ht="110" customHeight="1">
+      <x:c r="A233" s="241" t="str">
+        <x:v>API-EMP-002</x:v>
+      </x:c>
+      <x:c r="B233" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C233" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D233" s="241" t="str">
+        <x:v>response.body.data.managerName</x:v>
+      </x:c>
+      <x:c r="E233" s="241" t="str">
+        <x:v>String</x:v>
+      </x:c>
+      <x:c r="F233" s="241" t="str">
+        <x:v>任意</x:v>
+      </x:c>
+      <x:c r="G233" s="241" t="str">
+        <x:v>最大100</x:v>
+      </x:c>
+      <x:c r="H233" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I233" s="241" t="str">
+        <x:v>可</x:v>
+      </x:c>
+      <x:c r="J233" s="241" t="str">
+        <x:v>上司名。未指定はNull</x:v>
+      </x:c>
+      <x:c r="K233" s="241" t="str">
+        <x:v>employees.manager_idで社員名を参照</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="110" customHeight="1">
+      <x:c r="A234" s="241" t="str">
+        <x:v>API-EMP-002</x:v>
+      </x:c>
+      <x:c r="B234" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C234" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D234" s="241" t="str">
+        <x:v>response.body.data.retirementImpact</x:v>
+      </x:c>
+      <x:c r="E234" s="241" t="str">
+        <x:v>Object</x:v>
+      </x:c>
+      <x:c r="F234" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G234" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H234" s="241" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="I234" s="241" t="str">
+        <x:v>可</x:v>
+      </x:c>
+      <x:c r="J234" s="241" t="str">
+        <x:v>ADMINのみObject。他RoleはNull。画面上の取得値は参考であり退職時に再判定</x:v>
+      </x:c>
+      <x:c r="K234" s="241" t="str">
+        <x:v>projects/project_members/tasksを集計</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="110" customHeight="1">
+      <x:c r="A235" s="241" t="str">
+        <x:v>API-EMP-002</x:v>
+      </x:c>
+      <x:c r="B235" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C235" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D235" s="241" t="str">
+        <x:v>response.body.data.retirementImpact.pmProjectCount</x:v>
+      </x:c>
+      <x:c r="E235" s="241" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="F235" s="241" t="str">
+        <x:v>条件必須</x:v>
+      </x:c>
+      <x:c r="G235" s="241" t="str">
+        <x:v>0以上</x:v>
+      </x:c>
+      <x:c r="H235" s="241" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="I235" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J235" s="241" t="str">
+        <x:v>退職対象社員がPMの未削除PLANNING/IN_PROGRESS/SUSPENDED PJ件数</x:v>
+      </x:c>
+      <x:c r="K235" s="241" t="str">
+        <x:v>projects.manager_id/status/deleted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="110" customHeight="1">
+      <x:c r="A236" s="241" t="str">
+        <x:v>API-EMP-002</x:v>
+      </x:c>
+      <x:c r="B236" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C236" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D236" s="241" t="str">
+        <x:v>response.body.data.retirementImpact.activeMemberCount</x:v>
+      </x:c>
+      <x:c r="E236" s="241" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="F236" s="241" t="str">
+        <x:v>条件必須</x:v>
+      </x:c>
+      <x:c r="G236" s="241" t="str">
+        <x:v>0以上</x:v>
+      </x:c>
+      <x:c r="H236" s="241" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="I236" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J236" s="241" t="str">
+        <x:v>退職対象社員のACTIVE参加件数（未削除PJ）</x:v>
+      </x:c>
+      <x:c r="K236" s="241" t="str">
+        <x:v>project_members.employee_id/status、projects.deleted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="110" customHeight="1">
+      <x:c r="A237" s="241" t="str">
+        <x:v>API-EMP-002</x:v>
+      </x:c>
+      <x:c r="B237" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C237" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D237" s="241" t="str">
+        <x:v>response.body.data.retirementImpact.unfinishedTaskCount</x:v>
+      </x:c>
+      <x:c r="E237" s="241" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="F237" s="241" t="str">
+        <x:v>条件必須</x:v>
+      </x:c>
+      <x:c r="G237" s="241" t="str">
+        <x:v>0以上</x:v>
+      </x:c>
+      <x:c r="H237" s="241" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="I237" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J237" s="241" t="str">
+        <x:v>退職対象社員が担当する未削除TODO/IN_PROGRESS/REVIEW Task件数</x:v>
+      </x:c>
+      <x:c r="K237" s="241" t="str">
+        <x:v>tasks.assignee_id/status/deleted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="110" customHeight="1">
+      <x:c r="A238" s="241" t="str">
+        <x:v>API-EMP-002</x:v>
+      </x:c>
+      <x:c r="B238" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C238" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D238" s="241" t="str">
+        <x:v>response.body.data.projects[].status</x:v>
+      </x:c>
+      <x:c r="E238" s="241" t="str">
+        <x:v>String</x:v>
+      </x:c>
+      <x:c r="F238" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G238" s="241" t="str">
+        <x:v>最大20</x:v>
+      </x:c>
+      <x:c r="H238" s="241" t="str">
+        <x:v>PLANNING/IN_PROGRESS/SUSPENDED/COMPLETED/CANCELLED</x:v>
+      </x:c>
+      <x:c r="I238" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J238" s="241" t="str">
+        <x:v>PJ状態</x:v>
+      </x:c>
+      <x:c r="K238" s="241" t="str">
+        <x:v>projects.status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="110" customHeight="1">
+      <x:c r="A239" s="241" t="str">
+        <x:v>API-EMP-002</x:v>
+      </x:c>
+      <x:c r="B239" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C239" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D239" s="241" t="str">
+        <x:v>response.body.data.projects[].startDate</x:v>
+      </x:c>
+      <x:c r="E239" s="241" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="F239" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G239" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H239" s="241" t="str">
+        <x:v>yyyy-MM-dd</x:v>
+      </x:c>
+      <x:c r="I239" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J239" s="241" t="str">
+        <x:v>開始日</x:v>
+      </x:c>
+      <x:c r="K239" s="241" t="str">
+        <x:v>projects.start_date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="110" customHeight="1">
+      <x:c r="A240" s="241" t="str">
+        <x:v>API-EMP-002</x:v>
+      </x:c>
+      <x:c r="B240" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C240" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D240" s="241" t="str">
+        <x:v>response.body.data.projects[].memberStatus</x:v>
+      </x:c>
+      <x:c r="E240" s="241" t="str">
+        <x:v>String</x:v>
+      </x:c>
+      <x:c r="F240" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G240" s="241" t="str">
+        <x:v>最大20</x:v>
+      </x:c>
+      <x:c r="H240" s="241" t="str">
+        <x:v>ACTIVE/LEFT</x:v>
+      </x:c>
+      <x:c r="I240" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J240" s="241" t="str">
+        <x:v>対象社員の参加状態</x:v>
+      </x:c>
+      <x:c r="K240" s="241" t="str">
+        <x:v>project_members.status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="110" customHeight="1">
+      <x:c r="A241" s="241" t="str">
+        <x:v>API-EMP-002</x:v>
+      </x:c>
+      <x:c r="B241" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C241" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D241" s="241" t="str">
+        <x:v>response.body.data.tasks[].status</x:v>
+      </x:c>
+      <x:c r="E241" s="241" t="str">
+        <x:v>String</x:v>
+      </x:c>
+      <x:c r="F241" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G241" s="241" t="str">
+        <x:v>最大20</x:v>
+      </x:c>
+      <x:c r="H241" s="241" t="str">
+        <x:v>TODO/IN_PROGRESS/REVIEW/COMPLETED/CANCELLED</x:v>
+      </x:c>
+      <x:c r="I241" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J241" s="241" t="str">
+        <x:v>Task状態</x:v>
+      </x:c>
+      <x:c r="K241" s="241" t="str">
+        <x:v>tasks.status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="110" customHeight="1">
+      <x:c r="A242" s="241" t="str">
+        <x:v>API-EMP-002</x:v>
+      </x:c>
+      <x:c r="B242" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C242" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D242" s="241" t="str">
+        <x:v>response.body.data.tasks[].updatedAt</x:v>
+      </x:c>
+      <x:c r="E242" s="241" t="str">
+        <x:v>DateTime</x:v>
+      </x:c>
+      <x:c r="F242" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G242" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H242" s="241" t="str">
+        <x:v>ISO-8601</x:v>
+      </x:c>
+      <x:c r="I242" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J242" s="241" t="str">
+        <x:v>更新日時</x:v>
+      </x:c>
+      <x:c r="K242" s="241" t="str">
+        <x:v>tasks.updated_at</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:K2"/>
     <x:mergeCell ref="A6:K6"/>
-    <x:mergeCell ref="A219:K220"/>
     <x:mergeCell ref="A227:K228"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="82" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="100" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="100" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="38" hidden="0" customWidth="1"/>
@@ -12882,6 +13880,11 @@
       <x:c r="E1" s="172"/>
       <x:c r="F1" s="172"/>
       <x:c r="G1" s="172"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="172"/>
@@ -12891,6 +13894,11 @@
       <x:c r="E2" s="172"/>
       <x:c r="F2" s="172"/>
       <x:c r="G2" s="172"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="174" t="str">
@@ -12900,31 +13908,57 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="139"/>
-      <x:c r="D3" s="174" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="D3" s="248" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="E3" s="139" t="str">
         <x:v>CW-BD-11-SAMPLE</x:v>
       </x:c>
       <x:c r="F3" s="139"/>
       <x:c r="G3" s="139"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="174" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="63" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="E4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="139"/>
       <x:c r="G4" s="139"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="203" t="str">
+        <x:v>参考資料。Contract正本は23_API項目定義。Request例は送信区分別の表示用Object（そのまま送るJSONではない）。認証等の共通Headerは10／19参照。Binary PartはFile名で表記。各行は独立した例。</x:v>
+      </x:c>
+      <x:c r="B5" s="203"/>
+      <x:c r="C5" s="203"/>
+      <x:c r="D5" s="203"/>
+      <x:c r="E5" s="203"/>
+      <x:c r="F5" s="203"/>
+      <x:c r="G5" s="203"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="175" t="str">
@@ -12936,6 +13970,11 @@
       <x:c r="E6" s="175"/>
       <x:c r="F6" s="175"/>
       <x:c r="G6" s="175"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="181" t="str">
@@ -12959,8 +13998,13 @@
       <x:c r="G7" s="181" t="str">
         <x:v>備考</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="120" customHeight="1">
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
+    </x:row>
+    <x:row r="8" ht="115" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-EMP-001</x:v>
       </x:c>
@@ -12968,52 +14012,10 @@
         <x:v>従業員ページ検索</x:v>
       </x:c>
       <x:c r="C8" s="67" t="str">
-        <x:v>{
-  "query": {
-    "employeeCode": "sample",
-    "name": "サンプル",
-    "email": "user@example.co.jp",
-    "departmentId": 1001,
-    "joinedFrom": "2026-08-10",
-    "joinedTo": "2026-08-10",
-    "status": "EMPLOYED",
-    "page": 0,
-    "size": 20,
-    "sort": "sample"
-  }
-}</x:v>
+        <x:v>{"query": {"employeeCode": "sample", "name": "サンプル", "email": "user@example.co.jp", "departmentId": 1001, "joinedFrom": "2026-08-10", "joinedTo": "2026-08-10", "status": "EMPLOYED", "page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D8" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "content": [
-      {
-        "id": 1001,
-        "employeeCode": "sample",
-        "name": "サンプル",
-        "nameKana": "サンプル",
-        "email": "user@example.co.jp",
-        "departmentId": 1001,
-        "departmentName": "サンプル",
-        "position": "sample",
-        "employmentStatus": "EMPLOYED",
-        "joinedDate": "2026-08-10",
-        "leftDate": "2026-08-10",
-        "version": 1
-      }
-    ],
-    "page": 1,
-    "size": 1,
-    "totalElements": 1001,
-    "totalPages": 1,
-    "first": true,
-    "last": true
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"content": [{"id": 1001, "employeeCode": "sample", "name": "サンプル", "nameKana": "サンプル", "email": "user@example.co.jp", "departmentId": 1001, "departmentName": "サンプル", "position": "sample", "employmentStatus": "EMPLOYED", "joinedDate": "2026-08-10", "leftDate": null, "version": 1}], "page": 0, "size": 20, "totalElements": 1, "totalPages": 1, "first": true, "last": true}}</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
         <x:v>200</x:v>
@@ -13024,8 +14026,13 @@
       <x:c r="G8" s="67" t="str">
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="120" customHeight="1">
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+    </x:row>
+    <x:row r="9" ht="190" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-EMP-002</x:v>
       </x:c>
@@ -13033,55 +14040,10 @@
         <x:v>従業員詳細</x:v>
       </x:c>
       <x:c r="C9" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}}</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "employeeCode": "sample",
-    "name": "サンプル",
-    "nameKana": "サンプル",
-    "email": "user@example.co.jp",
-    "departmentId": 1001,
-    "departmentName": "サンプル",
-    "position": "sample",
-    "employmentStatus": "EMPLOYED",
-    "joinedDate": "2026-08-10",
-    "leftDate": "2026-08-10",
-    "version": 1,
-    "phone": "sample",
-    "managerId": 1001,
-    "remark": "sample",
-    "projects": [
-      {
-        "id": 1001,
-        "projectCode": "sample",
-        "name": "サンプル",
-        "managerId": 1001,
-        "managerName": "サンプル"
-      }
-    ],
-    "tasks": [
-      {
-        "id": 1001,
-        "taskCode": "sample",
-        "projectId": 1001,
-        "projectName": "サンプル",
-        "title": "sample",
-        "assigneeId": 1001
-      }
-    ]
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "employeeCode": "sample", "name": "サンプル", "nameKana": "サンプル", "email": "user@example.co.jp", "departmentId": 1001, "departmentName": "サンプル", "position": "sample", "employmentStatus": "EMPLOYED", "joinedDate": "2026-08-10", "leftDate": null, "version": 1, "phone": "03-1234-5678", "managerId": null, "remark": "sample", "projects": [{"id": 1001, "projectCode": "sample", "name": "サンプル", "managerId": 1002, "managerName": "サンプル", "status": "IN_PROGRESS", "startDate": "2026-08-01", "memberStatus": "ACTIVE"}], "tasks": [{"id": 1001, "taskCode": "sample", "projectId": 1001, "projectName": "サンプル", "title": "sample", "assigneeId": 1001, "status": "TODO", "updatedAt": "2026-08-10T09:00:00+09:00"}], "managerName": null, "retirementImpact": {"pmProjectCount": 1, "activeMemberCount": 1, "unfinishedTaskCount": 1}}}</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
         <x:v>200</x:v>
@@ -13092,8 +14054,13 @@
       <x:c r="G9" s="67" t="str">
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="120" customHeight="1">
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
+    </x:row>
+    <x:row r="10" ht="100" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-EMP-003</x:v>
       </x:c>
@@ -13101,41 +14068,10 @@
         <x:v>従業員登録</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
-        <x:v>{
-  "body": {
-    "employeeCode": "sample",
-    "name": "サンプル",
-    "nameKana": "サンプル",
-    "email": "user@example.co.jp",
-    "phone": "sample",
-    "departmentId": 1001,
-    "position": "sample",
-    "joinedDate": "2026-08-10",
-    "managerId": 1001,
-    "username": "サンプル",
-    "roleIds": [
-      1001,
-      1002
-    ],
-    "remark": "sample"
-  },
-  "header": {
-    "X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"
-  }
-}</x:v>
+        <x:v>{"body": {"employeeCode": "sample", "name": "サンプル", "nameKana": "サンプル", "email": "user@example.co.jp", "phone": "03-1234-5678", "departmentId": 1001, "position": "sample", "joinedDate": "2026-08-10", "managerId": 1002, "username": "サンプル", "roleIds": [1001, 1002], "remark": "sample"}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}}</x:v>
       </x:c>
       <x:c r="D10" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "employeeCode": "sample",
-    "temporaryPassword": "********"
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "employeeCode": "sample", "temporaryPassword": "Train9!Sample"}}</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
         <x:v>201</x:v>
@@ -13146,8 +14082,13 @@
       <x:c r="G10" s="67" t="str">
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="120" customHeight="1">
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+    </x:row>
+    <x:row r="11" ht="100" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-EMP-004</x:v>
       </x:c>
@@ -13155,34 +14096,10 @@
         <x:v>従業員更新</x:v>
       </x:c>
       <x:c r="C11" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "name": "サンプル",
-    "nameKana": "サンプル",
-    "email": "user@example.co.jp",
-    "phone": "sample",
-    "departmentId": 1001,
-    "position": "sample",
-    "managerId": 1001,
-    "remark": "sample",
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"name": "サンプル", "nameKana": "サンプル", "email": "user@example.co.jp", "phone": "03-1234-5678", "departmentId": 1001, "position": "sample", "managerId": 1002, "remark": "sample", "version": 1}}</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "version": 2}}</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
         <x:v>200</x:v>
@@ -13193,8 +14110,13 @@
       <x:c r="G11" s="67" t="str">
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="120" customHeight="1">
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+    </x:row>
+    <x:row r="12" ht="100" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-EMP-005</x:v>
       </x:c>
@@ -13202,31 +14124,10 @@
         <x:v>従業員状態変更</x:v>
       </x:c>
       <x:c r="C12" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "status": "LEFT",
-    "leftDate": "2026-08-10",
-    "unfinishedTaskPolicy": "REASSIGN",
-    "version": 1,
-    "reassignmentAssigneeId": 1002
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"status": "LEFT", "leftDate": "2026-08-10", "unfinishedTaskPolicy": "REASSIGN", "version": 1, "reassignmentAssigneeId": 1002}}</x:v>
       </x:c>
       <x:c r="D12" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "status": "EMPLOYED",
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "status": "LEFT", "version": 2}}</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
         <x:v>200</x:v>
@@ -13237,8 +14138,13 @@
       <x:c r="G12" s="67" t="str">
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="120" customHeight="1">
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13" ht="100" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-EMP-006</x:v>
       </x:c>
@@ -13246,35 +14152,10 @@
         <x:v>従業員Excel取込</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
-        <x:v>{
-  "multipart": {
-    "file": "sample"
-  },
-  "header": {
-    "X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"
-  }
-}</x:v>
+        <x:v>{"multipart": {"file": "employees.xlsx（Binary Part）"}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}}</x:v>
       </x:c>
       <x:c r="D13" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "total": 1,
-    "success": 1,
-    "failed": 1,
-    "errors": [
-      {
-        "row": "sample",
-        "field": "sample",
-        "code": "COMMON-0000",
-        "message": "処理成功"
-      }
-    ]
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"total": 1, "success": 1, "failed": 0, "successes": [{"row": 2, "employeeCode": "EMP0001", "temporaryPassword": "Train9!Sample"}], "errors": []}}</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
         <x:v>201</x:v>
@@ -13283,10 +14164,15 @@
         <x:v>application/json</x:v>
       </x:c>
       <x:c r="G13" s="67" t="str">
-        <x:v>値は例。項目定義を正とする</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="120" customHeight="1">
+        <x:v>値は例。項目定義を正とする。全行成功例。2行目の新規社員登録成功。File全体不正は共通Error Response。</x:v>
+      </x:c>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14" ht="100" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-EMP-007</x:v>
       </x:c>
@@ -13294,20 +14180,7 @@
         <x:v>従業員Excel出力</x:v>
       </x:c>
       <x:c r="C14" s="67" t="str">
-        <x:v>{
-  "query": {
-    "employeeCode": "sample",
-    "name": "サンプル",
-    "email": "user@example.co.jp",
-    "departmentId": 1001,
-    "joinedFrom": "2026-08-10",
-    "joinedTo": "2026-08-10",
-    "status": "EMPLOYED",
-    "page": 0,
-    "size": 20,
-    "sort": "sample"
-  }
-}</x:v>
+        <x:v>{"query": {"employeeCode": "sample", "name": "サンプル", "email": "user@example.co.jp", "departmentId": 1001, "joinedFrom": "2026-08-10", "joinedTo": "2026-08-10", "status": "EMPLOYED", "page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D14" s="67" t="str">
         <x:v>&lt;binary stream&gt;</x:v>
@@ -13316,13 +14189,18 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="F14" s="67" t="str">
-        <x:v>binary</x:v>
+        <x:v>application/vnd.openxmlformats-officedocument.spreadsheetml.sheet</x:v>
       </x:c>
       <x:c r="G14" s="67" t="str">
-        <x:v>値は例。項目定義を正とする</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="120" customHeight="1">
+        <x:v>値は例。項目定義を正とする。Content-Disposition: attachment; filename="employees.xlsx"; filename*=UTF-8''employees.xlsx。BodyはBinary。</x:v>
+      </x:c>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15" ht="100" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-DEPT-001</x:v>
       </x:c>
@@ -13330,44 +14208,10 @@
         <x:v>部門Tree取得</x:v>
       </x:c>
       <x:c r="C15" s="67" t="str">
-        <x:v>{
-  "query": {
-    "includeDisabled": true
-  }
-}</x:v>
+        <x:v>{"query": {"includeDisabled": true}}</x:v>
       </x:c>
       <x:c r="D15" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "departments": [
-      {
-        "id": 1001,
-        "departmentCode": "sample",
-        "name": "サンプル",
-        "parentId": 1001,
-        "managerId": 1001,
-        "displayOrder": 1,
-        "status": "ACTIVE",
-        "children": [
-          {
-            "id": 11,
-            "departmentCode": "DEV-01",
-            "name": "開発一課",
-            "managerId": 1001,
-            "displayOrder": 1,
-            "status": "ACTIVE",
-            "childrenCount": 0
-          }
-        ],
-        "version": 1
-      }
-    ]
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"departments": [{"id": 1001, "departmentCode": "sample", "name": "サンプル", "parentId": null, "managerId": 1001, "displayOrder": 1, "status": "ACTIVE", "children": [{"id": 11, "departmentCode": "DEV-01", "name": "開発一課", "managerId": 1001, "displayOrder": 1, "status": "ACTIVE", "childrenCount": 0}], "version": 1}]}}</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
         <x:v>200</x:v>
@@ -13378,8 +14222,13 @@
       <x:c r="G15" s="67" t="str">
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="120" customHeight="1">
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16" ht="100" customHeight="1">
       <x:c r="A16" s="67" t="str">
         <x:v>API-DEPT-002</x:v>
       </x:c>
@@ -13387,29 +14236,10 @@
         <x:v>部門詳細</x:v>
       </x:c>
       <x:c r="C16" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}}</x:v>
       </x:c>
       <x:c r="D16" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "code": "COMMON-0000",
-    "name": "サンプル",
-    "parentId": 1001,
-    "managerId": 1001,
-    "displayOrder": 1,
-    "status": "ACTIVE",
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "code": "D001", "name": "営業部", "parentId": 1000, "managerId": 1001, "displayOrder": 1, "status": "ACTIVE", "version": 1}}</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
         <x:v>200</x:v>
@@ -13418,10 +14248,15 @@
         <x:v>application/json</x:v>
       </x:c>
       <x:c r="G16" s="67" t="str">
-        <x:v>値は例。項目定義を正とする</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="120" customHeight="1">
+        <x:v>値は例。項目定義を正とする。非Root部門の例（親部門ID=1000）。</x:v>
+      </x:c>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="100" customHeight="1">
       <x:c r="A17" s="67" t="str">
         <x:v>API-DEPT-003</x:v>
       </x:c>
@@ -13429,31 +14264,10 @@
         <x:v>部門登録</x:v>
       </x:c>
       <x:c r="C17" s="67" t="str">
-        <x:v>{
-  "body": {
-    "departmentCode": "sample",
-    "name": "サンプル",
-    "parentId": 1001,
-    "managerId": 1001,
-    "displayOrder": 1,
-    "status": "ACTIVE"
-  },
-  "header": {
-    "X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"
-  }
-}</x:v>
+        <x:v>{"body": {"departmentCode": "sample", "name": "サンプル", "parentId": 1000, "managerId": 1001, "displayOrder": 1, "status": "ACTIVE"}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}}</x:v>
       </x:c>
       <x:c r="D17" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "version": 1}}</x:v>
       </x:c>
       <x:c r="E17" s="67" t="str">
         <x:v>201</x:v>
@@ -13464,8 +14278,13 @@
       <x:c r="G17" s="67" t="str">
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="120" customHeight="1">
+      <x:c r="H17"/>
+      <x:c r="I17"/>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
+    </x:row>
+    <x:row r="18" ht="100" customHeight="1">
       <x:c r="A18" s="67" t="str">
         <x:v>API-DEPT-004</x:v>
       </x:c>
@@ -13473,31 +14292,10 @@
         <x:v>部門更新</x:v>
       </x:c>
       <x:c r="C18" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "name": "サンプル",
-    "parentId": 1001,
-    "managerId": 1001,
-    "displayOrder": 1,
-    "status": "ACTIVE",
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"name": "サンプル", "parentId": 1000, "managerId": 1001, "displayOrder": 1, "status": "ACTIVE", "version": 1}}</x:v>
       </x:c>
       <x:c r="D18" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "version": 2}}</x:v>
       </x:c>
       <x:c r="E18" s="67" t="str">
         <x:v>200</x:v>
@@ -13508,8 +14306,13 @@
       <x:c r="G18" s="67" t="str">
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" ht="120" customHeight="1">
+      <x:c r="H18"/>
+      <x:c r="I18"/>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
+    </x:row>
+    <x:row r="19" ht="100" customHeight="1">
       <x:c r="A19" s="67" t="str">
         <x:v>API-DEPT-005</x:v>
       </x:c>
@@ -13517,14 +14320,7 @@
         <x:v>部門削除</x:v>
       </x:c>
       <x:c r="C19" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "query": {
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "query": {"version": 1}}</x:v>
       </x:c>
       <x:c r="D19" s="67" t="str">
         <x:v>-（Response Bodyなし）</x:v>
@@ -13538,6 +14334,25 @@
       <x:c r="G19" s="67" t="str">
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
+      <x:c r="H19"/>
+      <x:c r="I19"/>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="186" t="str">
@@ -13549,6 +14364,11 @@
       <x:c r="E21" s="186"/>
       <x:c r="F21" s="186"/>
       <x:c r="G21" s="186"/>
+      <x:c r="H21"/>
+      <x:c r="I21"/>
+      <x:c r="J21"/>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="186"/>
@@ -13558,6 +14378,34 @@
       <x:c r="E22" s="186"/>
       <x:c r="F22" s="186"/>
       <x:c r="G22" s="186"/>
+      <x:c r="H22"/>
+      <x:c r="I22"/>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
+    </x:row>
+    <x:row r="23" ht="220" customHeight="1">
+      <x:c r="A23" s="247" t="str">
+        <x:v>API-EMP-006</x:v>
+      </x:c>
+      <x:c r="B23" s="247" t="str">
+        <x:v>従業員Excel取込（部分成功）</x:v>
+      </x:c>
+      <x:c r="C23" s="247" t="str">
+        <x:v>{"multipart": {"file": "employees.xlsx（Binary Part）"}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}}</x:v>
+      </x:c>
+      <x:c r="D23" s="247" t="str">
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"total": 2, "success": 1, "failed": 1, "successes": [{"row": 2, "employeeCode": "EMP0001", "temporaryPassword": "Train9!Sample"}], "errors": [{"row": 3, "field": "employeeCode", "code": "EMP-4001", "message": "入力または処理内容を確認してください。"}]}}</x:v>
+      </x:c>
+      <x:c r="E23" s="247" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="F23" s="247" t="str">
+        <x:v>application/json</x:v>
+      </x:c>
+      <x:c r="G23" s="247" t="str">
+        <x:v>2行目EMP0001は新規成功。3行目EMP0002はDB既存番号重複。成功行Commit、失敗行Rollback。EMP-4001→18／31B MSG-E-019。成功件数1、失敗件数1。HTTPは現行10／19の登録201に従う。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
